--- a/data/templates/Ram 2026_Owen Testing.xlsx
+++ b/data/templates/Ram 2026_Owen Testing.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -2292,6 +2292,12 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2300,21 +2306,6 @@
     </xf>
     <xf numFmtId="3" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -2333,6 +2324,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2962,10 +2962,10 @@
       <c r="U7" s="14"/>
     </row>
     <row r="8" spans="1:77" x14ac:dyDescent="0.25">
-      <c r="A8" s="144" t="s">
+      <c r="A8" s="138" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="145"/>
+      <c r="B8" s="139"/>
       <c r="C8" s="78"/>
       <c r="D8" s="83" t="s">
         <v>8</v>
@@ -3052,106 +3052,106 @@
       <c r="I13" s="68"/>
       <c r="J13" s="68"/>
       <c r="K13" s="72"/>
-      <c r="L13" s="146" t="s">
+      <c r="L13" s="143" t="s">
         <v>14</v>
       </c>
-      <c r="M13" s="147"/>
-      <c r="N13" s="138" cm="1">
+      <c r="M13" s="144"/>
+      <c r="N13" s="140" cm="1">
         <f t="array" ref="N13">SUM(Q17:Q65)+SUM(_xlfn._xlws.FILTER(P17:P65,Q17:Q65=""))+SUM(_xlfn._xlws.FILTER(O17:O65,(P17:P65="")*(Q17:Q65="")))+SUMIFS(R17:R65,Q17:Q65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(N17:N65)</f>
         <v>685594.25000000012</v>
       </c>
-      <c r="O13" s="139"/>
-      <c r="P13" s="139"/>
-      <c r="Q13" s="139"/>
-      <c r="R13" s="140"/>
-      <c r="S13" s="138" cm="1">
+      <c r="O13" s="141"/>
+      <c r="P13" s="141"/>
+      <c r="Q13" s="141"/>
+      <c r="R13" s="142"/>
+      <c r="S13" s="140" cm="1">
         <f t="array" ref="S13">SUM(V17:V65)+SUM(_xlfn._xlws.FILTER(U17:U65,V17:V65=""))+SUM(_xlfn._xlws.FILTER(T17:T65,(U17:U65="")*(V17:V65="")))+SUMIFS(W17:W65,V17:V65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(S17:S65)</f>
         <v>891985.88</v>
       </c>
-      <c r="T13" s="139"/>
-      <c r="U13" s="139"/>
-      <c r="V13" s="139"/>
-      <c r="W13" s="140"/>
-      <c r="X13" s="138" cm="1">
+      <c r="T13" s="141"/>
+      <c r="U13" s="141"/>
+      <c r="V13" s="141"/>
+      <c r="W13" s="142"/>
+      <c r="X13" s="140" cm="1">
         <f t="array" ref="X13">SUM(AA17:AA65)+SUM(_xlfn._xlws.FILTER(Z17:Z65,AA17:AA65=""))+SUM(_xlfn._xlws.FILTER(Y17:Y65,(Z17:Z65="")*(AA17:AA65="")))+SUMIFS(AB17:AB65,AA17:AA65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(X17:X65)</f>
         <v>647579.66999999993</v>
       </c>
-      <c r="Y13" s="139"/>
-      <c r="Z13" s="139"/>
-      <c r="AA13" s="139"/>
-      <c r="AB13" s="140"/>
-      <c r="AC13" s="138" cm="1">
+      <c r="Y13" s="141"/>
+      <c r="Z13" s="141"/>
+      <c r="AA13" s="141"/>
+      <c r="AB13" s="142"/>
+      <c r="AC13" s="140" cm="1">
         <f t="array" ref="AC13">SUM(AF17:AF65)+SUM(_xlfn._xlws.FILTER(AE17:AE65,AF17:AF65=""))+SUM(_xlfn._xlws.FILTER(AD17:AD65,(AE17:AE65="")*(AF17:AF65="")))+SUMIFS(AG17:AG65,AF17:AF65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(AC17:AC65)</f>
         <v>647579.66999999993</v>
       </c>
-      <c r="AD13" s="139"/>
-      <c r="AE13" s="139"/>
-      <c r="AF13" s="139"/>
-      <c r="AG13" s="140"/>
-      <c r="AH13" s="138" cm="1">
+      <c r="AD13" s="141"/>
+      <c r="AE13" s="141"/>
+      <c r="AF13" s="141"/>
+      <c r="AG13" s="142"/>
+      <c r="AH13" s="140" cm="1">
         <f t="array" ref="AH13">SUM(AK17:AK65)+SUM(_xlfn._xlws.FILTER(AJ17:AJ65,AK17:AK65=""))+SUM(_xlfn._xlws.FILTER(AI17:AI65,(AJ17:AJ65="")*(AK17:AK65="")))+SUMIFS(AL17:AL65,AK17:AK65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(AH17:AH65)</f>
         <v>645269.66999999993</v>
       </c>
-      <c r="AI13" s="139"/>
-      <c r="AJ13" s="139"/>
-      <c r="AK13" s="139"/>
-      <c r="AL13" s="140"/>
-      <c r="AM13" s="138" cm="1">
+      <c r="AI13" s="141"/>
+      <c r="AJ13" s="141"/>
+      <c r="AK13" s="141"/>
+      <c r="AL13" s="142"/>
+      <c r="AM13" s="140" cm="1">
         <f t="array" ref="AM13">SUM(AP17:AP65)+SUM(_xlfn._xlws.FILTER(AO17:AO65,AP17:AP65=""))+SUM(_xlfn._xlws.FILTER(AN17:AN65,(AO17:AO65="")*(AP17:AP65="")))+SUMIFS(AQ17:AQ65,AP17:AP65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(AM17:AM65)</f>
         <v>635449.66999999993</v>
       </c>
-      <c r="AN13" s="139"/>
-      <c r="AO13" s="139"/>
-      <c r="AP13" s="139"/>
-      <c r="AQ13" s="140"/>
-      <c r="AR13" s="138" cm="1">
+      <c r="AN13" s="141"/>
+      <c r="AO13" s="141"/>
+      <c r="AP13" s="141"/>
+      <c r="AQ13" s="142"/>
+      <c r="AR13" s="140" cm="1">
         <f t="array" ref="AR13">SUM(AU17:AU65)+SUM(_xlfn._xlws.FILTER(AT17:AT65,AU17:AU65=""))+SUM(_xlfn._xlws.FILTER(AS17:AS65,(AT17:AT65="")*(AU17:AU65="")))+SUMIFS(AV17:AV65,AU17:AU65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(AR17:AR65)</f>
         <v>635449.66999999993</v>
       </c>
-      <c r="AS13" s="139"/>
-      <c r="AT13" s="139"/>
-      <c r="AU13" s="139"/>
-      <c r="AV13" s="140"/>
-      <c r="AW13" s="138" cm="1">
+      <c r="AS13" s="141"/>
+      <c r="AT13" s="141"/>
+      <c r="AU13" s="141"/>
+      <c r="AV13" s="142"/>
+      <c r="AW13" s="140" cm="1">
         <f t="array" ref="AW13">SUM(AZ17:AZ65)+SUM(_xlfn._xlws.FILTER(AY17:AY65,AZ17:AZ65=""))+SUM(_xlfn._xlws.FILTER(AX17:AX65,(AY17:AY65="")*(AZ17:AZ65="")))+SUMIFS(BA17:BA65,AZ17:AZ65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(AW17:AW65)</f>
         <v>635449.66999999993</v>
       </c>
-      <c r="AX13" s="139"/>
-      <c r="AY13" s="139"/>
-      <c r="AZ13" s="139"/>
-      <c r="BA13" s="140"/>
-      <c r="BB13" s="138" cm="1">
+      <c r="AX13" s="141"/>
+      <c r="AY13" s="141"/>
+      <c r="AZ13" s="141"/>
+      <c r="BA13" s="142"/>
+      <c r="BB13" s="140" cm="1">
         <f t="array" ref="BB13">SUM(BE17:BE65)+SUM(_xlfn._xlws.FILTER(BD17:BD65,BE17:BE65=""))+SUM(_xlfn._xlws.FILTER(BC17:BC65,(BD17:BD65="")*(BE17:BE65="")))+SUMIFS(BF17:BF65,BE17:BE65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(BB17:BB65)</f>
         <v>635449.66999999993</v>
       </c>
-      <c r="BC13" s="139"/>
-      <c r="BD13" s="139"/>
-      <c r="BE13" s="139"/>
-      <c r="BF13" s="140"/>
-      <c r="BG13" s="138" cm="1">
+      <c r="BC13" s="141"/>
+      <c r="BD13" s="141"/>
+      <c r="BE13" s="141"/>
+      <c r="BF13" s="142"/>
+      <c r="BG13" s="140" cm="1">
         <f t="array" ref="BG13">SUM(BJ17:BJ65)+SUM(_xlfn._xlws.FILTER(BI17:BI65,BJ17:BJ65=""))+SUM(_xlfn._xlws.FILTER(BH17:BH65,(BI17:BI65="")*(BJ17:BJ65="")))+SUMIFS(BK17:BK65,BJ17:BJ65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(BG17:BG65)</f>
         <v>635449.66999999993</v>
       </c>
-      <c r="BH13" s="139"/>
-      <c r="BI13" s="139"/>
-      <c r="BJ13" s="139"/>
-      <c r="BK13" s="140"/>
-      <c r="BL13" s="138" cm="1">
+      <c r="BH13" s="141"/>
+      <c r="BI13" s="141"/>
+      <c r="BJ13" s="141"/>
+      <c r="BK13" s="142"/>
+      <c r="BL13" s="140" cm="1">
         <f t="array" ref="BL13">SUM(BO17:BO65)+SUM(_xlfn._xlws.FILTER(BN17:BN65,BO17:BO65=""))+SUM(_xlfn._xlws.FILTER(BM17:BM65,(BN17:BN65="")*(BO17:BO65="")))+SUMIFS(BP17:BP65,BO17:BO65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(BL17:BL65)</f>
         <v>635449.66999999993</v>
       </c>
-      <c r="BM13" s="139"/>
-      <c r="BN13" s="139"/>
-      <c r="BO13" s="139"/>
-      <c r="BP13" s="140"/>
-      <c r="BQ13" s="138" cm="1">
+      <c r="BM13" s="141"/>
+      <c r="BN13" s="141"/>
+      <c r="BO13" s="141"/>
+      <c r="BP13" s="142"/>
+      <c r="BQ13" s="140" cm="1">
         <f t="array" ref="BQ13">SUM(BT17:BT65)+SUM(_xlfn._xlws.FILTER(BS17:BS65,BT17:BT65=""))+SUM(_xlfn._xlws.FILTER(BR17:BR65,(BS17:BS65="")*(BT17:BT65="")))+SUMIFS(BU17:BU65,BT17:BT65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(BQ17:BQ65)</f>
         <v>635449.66999999993</v>
       </c>
-      <c r="BR13" s="139"/>
-      <c r="BS13" s="139"/>
-      <c r="BT13" s="139"/>
-      <c r="BU13" s="140"/>
+      <c r="BR13" s="141"/>
+      <c r="BS13" s="141"/>
+      <c r="BT13" s="141"/>
+      <c r="BU13" s="142"/>
       <c r="BV13" s="16" t="s">
         <v>15</v>
       </c>
@@ -3173,106 +3173,106 @@
       <c r="K14" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="L14" s="148" t="s">
+      <c r="L14" s="145" t="s">
         <v>17</v>
       </c>
-      <c r="M14" s="149"/>
-      <c r="N14" s="138" cm="1">
+      <c r="M14" s="146"/>
+      <c r="N14" s="140" cm="1">
         <f t="array" ref="N14">SUM(Q17:Q65)+SUM(_xlfn._xlws.FILTER(P17:P65,Q17:Q65=""))+SUM(_xlfn._xlws.FILTER(O17:O65,(P17:P65="")*(Q17:Q65="")))</f>
         <v>674619.25000000012</v>
       </c>
-      <c r="O14" s="139"/>
-      <c r="P14" s="139"/>
-      <c r="Q14" s="139"/>
-      <c r="R14" s="140"/>
-      <c r="S14" s="138" cm="1">
+      <c r="O14" s="141"/>
+      <c r="P14" s="141"/>
+      <c r="Q14" s="141"/>
+      <c r="R14" s="142"/>
+      <c r="S14" s="140" cm="1">
         <f t="array" ref="S14">SUM(V17:V65)+SUM(_xlfn._xlws.FILTER(U17:U65,V17:V65=""))+SUM(_xlfn._xlws.FILTER(T17:T65,(U17:U65="")*(V17:V65="")))</f>
         <v>871752.88</v>
       </c>
-      <c r="T14" s="139"/>
-      <c r="U14" s="139"/>
-      <c r="V14" s="139"/>
-      <c r="W14" s="140"/>
-      <c r="X14" s="138" cm="1">
+      <c r="T14" s="141"/>
+      <c r="U14" s="141"/>
+      <c r="V14" s="141"/>
+      <c r="W14" s="142"/>
+      <c r="X14" s="140" cm="1">
         <f t="array" ref="X14">SUM(AA17:AA65)+SUM(_xlfn._xlws.FILTER(Z17:Z65,AA17:AA65=""))+SUM(_xlfn._xlws.FILTER(Y17:Y65,(Z17:Z65="")*(AA17:AA65="")))</f>
         <v>647579.66999999993</v>
       </c>
-      <c r="Y14" s="139"/>
-      <c r="Z14" s="139"/>
-      <c r="AA14" s="139"/>
-      <c r="AB14" s="140"/>
-      <c r="AC14" s="138" cm="1">
+      <c r="Y14" s="141"/>
+      <c r="Z14" s="141"/>
+      <c r="AA14" s="141"/>
+      <c r="AB14" s="142"/>
+      <c r="AC14" s="140" cm="1">
         <f t="array" ref="AC14">SUM(AF17:AF65)+SUM(_xlfn._xlws.FILTER(AE17:AE65,AF17:AF65=""))+SUM(_xlfn._xlws.FILTER(AD17:AD65,(AE17:AE65="")*(AF17:AF65="")))</f>
         <v>647579.66999999993</v>
       </c>
-      <c r="AD14" s="139"/>
-      <c r="AE14" s="139"/>
-      <c r="AF14" s="139"/>
-      <c r="AG14" s="140"/>
-      <c r="AH14" s="138" cm="1">
+      <c r="AD14" s="141"/>
+      <c r="AE14" s="141"/>
+      <c r="AF14" s="141"/>
+      <c r="AG14" s="142"/>
+      <c r="AH14" s="140" cm="1">
         <f t="array" ref="AH14">SUM(AK17:AK65)+SUM(_xlfn._xlws.FILTER(AJ17:AJ65,AK17:AK65=""))+SUM(_xlfn._xlws.FILTER(AI17:AI65,(AJ17:AJ65="")*(AK17:AK65="")))</f>
         <v>645269.66999999993</v>
       </c>
-      <c r="AI14" s="139"/>
-      <c r="AJ14" s="139"/>
-      <c r="AK14" s="139"/>
-      <c r="AL14" s="140"/>
-      <c r="AM14" s="138" cm="1">
+      <c r="AI14" s="141"/>
+      <c r="AJ14" s="141"/>
+      <c r="AK14" s="141"/>
+      <c r="AL14" s="142"/>
+      <c r="AM14" s="140" cm="1">
         <f t="array" ref="AM14">SUM(AP17:AP65)+SUM(_xlfn._xlws.FILTER(AO17:AO65,AP17:AP65=""))+SUM(_xlfn._xlws.FILTER(AN17:AN65,(AO17:AO65="")*(AP17:AP65="")))</f>
         <v>635449.66999999993</v>
       </c>
-      <c r="AN14" s="139"/>
-      <c r="AO14" s="139"/>
-      <c r="AP14" s="139"/>
-      <c r="AQ14" s="140"/>
-      <c r="AR14" s="138" cm="1">
+      <c r="AN14" s="141"/>
+      <c r="AO14" s="141"/>
+      <c r="AP14" s="141"/>
+      <c r="AQ14" s="142"/>
+      <c r="AR14" s="140" cm="1">
         <f t="array" ref="AR14">SUM(AU17:AU65)+SUM(_xlfn._xlws.FILTER(AT17:AT65,AU17:AU65=""))+SUM(_xlfn._xlws.FILTER(AS17:AS65,(AT17:AT65="")*(AU17:AU65="")))</f>
         <v>635449.66999999993</v>
       </c>
-      <c r="AS14" s="139"/>
-      <c r="AT14" s="139"/>
-      <c r="AU14" s="139"/>
-      <c r="AV14" s="140"/>
-      <c r="AW14" s="138" cm="1">
+      <c r="AS14" s="141"/>
+      <c r="AT14" s="141"/>
+      <c r="AU14" s="141"/>
+      <c r="AV14" s="142"/>
+      <c r="AW14" s="140" cm="1">
         <f t="array" ref="AW14">SUM(AZ17:AZ65)+SUM(_xlfn._xlws.FILTER(AY17:AY65,AZ17:AZ65=""))+SUM(_xlfn._xlws.FILTER(AX17:AX65,(AY17:AY65="")*(AZ17:AZ65="")))</f>
         <v>635449.66999999993</v>
       </c>
-      <c r="AX14" s="139"/>
-      <c r="AY14" s="139"/>
-      <c r="AZ14" s="139"/>
-      <c r="BA14" s="140"/>
-      <c r="BB14" s="138" cm="1">
+      <c r="AX14" s="141"/>
+      <c r="AY14" s="141"/>
+      <c r="AZ14" s="141"/>
+      <c r="BA14" s="142"/>
+      <c r="BB14" s="140" cm="1">
         <f t="array" ref="BB14">SUM(BE17:BE65)+SUM(_xlfn._xlws.FILTER(BD17:BD65,BE17:BE65=""))+SUM(_xlfn._xlws.FILTER(BC17:BC65,(BD17:BD65="")*(BE17:BE65="")))</f>
         <v>635449.66999999993</v>
       </c>
-      <c r="BC14" s="139"/>
-      <c r="BD14" s="139"/>
-      <c r="BE14" s="139"/>
-      <c r="BF14" s="140"/>
-      <c r="BG14" s="138" cm="1">
+      <c r="BC14" s="141"/>
+      <c r="BD14" s="141"/>
+      <c r="BE14" s="141"/>
+      <c r="BF14" s="142"/>
+      <c r="BG14" s="140" cm="1">
         <f t="array" ref="BG14">SUM(BJ17:BJ65)+SUM(_xlfn._xlws.FILTER(BI17:BI65,BJ17:BJ65=""))+SUM(_xlfn._xlws.FILTER(BH17:BH65,(BI17:BI65="")*(BJ17:BJ65="")))</f>
         <v>635449.66999999993</v>
       </c>
-      <c r="BH14" s="139"/>
-      <c r="BI14" s="139"/>
-      <c r="BJ14" s="139"/>
-      <c r="BK14" s="140"/>
-      <c r="BL14" s="138" cm="1">
+      <c r="BH14" s="141"/>
+      <c r="BI14" s="141"/>
+      <c r="BJ14" s="141"/>
+      <c r="BK14" s="142"/>
+      <c r="BL14" s="140" cm="1">
         <f t="array" ref="BL14">SUM(BO17:BO65)+SUM(_xlfn._xlws.FILTER(BN17:BN65,BO17:BO65=""))+SUM(_xlfn._xlws.FILTER(BM17:BM65,(BN17:BN65="")*(BO17:BO65="")))</f>
         <v>635449.66999999993</v>
       </c>
-      <c r="BM14" s="139"/>
-      <c r="BN14" s="139"/>
-      <c r="BO14" s="139"/>
-      <c r="BP14" s="140"/>
-      <c r="BQ14" s="138" cm="1">
+      <c r="BM14" s="141"/>
+      <c r="BN14" s="141"/>
+      <c r="BO14" s="141"/>
+      <c r="BP14" s="142"/>
+      <c r="BQ14" s="140" cm="1">
         <f t="array" ref="BQ14">SUM(BT17:BT65)+SUM(_xlfn._xlws.FILTER(BS17:BS65,BT17:BT65=""))+SUM(_xlfn._xlws.FILTER(BR17:BR65,(BS17:BS65="")*(BT17:BT65="")))</f>
         <v>635449.66999999993</v>
       </c>
-      <c r="BR14" s="139"/>
-      <c r="BS14" s="139"/>
-      <c r="BT14" s="139"/>
-      <c r="BU14" s="140"/>
+      <c r="BR14" s="141"/>
+      <c r="BS14" s="141"/>
+      <c r="BT14" s="141"/>
+      <c r="BU14" s="142"/>
       <c r="BV14" s="16"/>
       <c r="BW14" s="17"/>
     </row>
@@ -3284,116 +3284,116 @@
         <f>SUBTOTAL(9,K17:K68)</f>
         <v>8537304.5</v>
       </c>
-      <c r="L15" s="150" t="s">
+      <c r="L15" s="147" t="s">
         <v>19</v>
       </c>
-      <c r="M15" s="151"/>
-      <c r="N15" s="141">
+      <c r="M15" s="148"/>
+      <c r="N15" s="149">
         <v>46053</v>
       </c>
-      <c r="O15" s="142" t="s">
+      <c r="O15" s="150" t="s">
         <v>20</v>
       </c>
-      <c r="P15" s="142"/>
-      <c r="Q15" s="142"/>
-      <c r="R15" s="142"/>
-      <c r="S15" s="141" t="s">
+      <c r="P15" s="150"/>
+      <c r="Q15" s="150"/>
+      <c r="R15" s="150"/>
+      <c r="S15" s="149" t="s">
         <v>21</v>
       </c>
-      <c r="T15" s="142"/>
-      <c r="U15" s="142"/>
-      <c r="V15" s="142"/>
-      <c r="W15" s="143"/>
-      <c r="X15" s="141">
+      <c r="T15" s="150"/>
+      <c r="U15" s="150"/>
+      <c r="V15" s="150"/>
+      <c r="W15" s="151"/>
+      <c r="X15" s="149">
         <v>46112</v>
       </c>
-      <c r="Y15" s="142" t="s">
+      <c r="Y15" s="150" t="s">
         <v>22</v>
       </c>
-      <c r="Z15" s="142"/>
-      <c r="AA15" s="142"/>
-      <c r="AB15" s="143"/>
-      <c r="AC15" s="141">
+      <c r="Z15" s="150"/>
+      <c r="AA15" s="150"/>
+      <c r="AB15" s="151"/>
+      <c r="AC15" s="149">
         <v>46142</v>
       </c>
-      <c r="AD15" s="142" t="s">
+      <c r="AD15" s="150" t="s">
         <v>23</v>
       </c>
-      <c r="AE15" s="142"/>
-      <c r="AF15" s="142"/>
-      <c r="AG15" s="143"/>
-      <c r="AH15" s="141">
+      <c r="AE15" s="150"/>
+      <c r="AF15" s="150"/>
+      <c r="AG15" s="151"/>
+      <c r="AH15" s="149">
         <v>46173</v>
       </c>
-      <c r="AI15" s="142" t="s">
+      <c r="AI15" s="150" t="s">
         <v>24</v>
       </c>
-      <c r="AJ15" s="142"/>
-      <c r="AK15" s="142"/>
-      <c r="AL15" s="143"/>
-      <c r="AM15" s="141">
+      <c r="AJ15" s="150"/>
+      <c r="AK15" s="150"/>
+      <c r="AL15" s="151"/>
+      <c r="AM15" s="149">
         <v>46203</v>
       </c>
-      <c r="AN15" s="142" t="s">
+      <c r="AN15" s="150" t="s">
         <v>25</v>
       </c>
-      <c r="AO15" s="142"/>
-      <c r="AP15" s="142"/>
-      <c r="AQ15" s="143"/>
-      <c r="AR15" s="141">
+      <c r="AO15" s="150"/>
+      <c r="AP15" s="150"/>
+      <c r="AQ15" s="151"/>
+      <c r="AR15" s="149">
         <v>46234</v>
       </c>
-      <c r="AS15" s="142" t="s">
+      <c r="AS15" s="150" t="s">
         <v>26</v>
       </c>
-      <c r="AT15" s="142"/>
-      <c r="AU15" s="142"/>
-      <c r="AV15" s="143"/>
-      <c r="AW15" s="141">
+      <c r="AT15" s="150"/>
+      <c r="AU15" s="150"/>
+      <c r="AV15" s="151"/>
+      <c r="AW15" s="149">
         <v>46265</v>
       </c>
-      <c r="AX15" s="142" t="s">
+      <c r="AX15" s="150" t="s">
         <v>27</v>
       </c>
-      <c r="AY15" s="142"/>
-      <c r="AZ15" s="142"/>
-      <c r="BA15" s="143"/>
-      <c r="BB15" s="141">
+      <c r="AY15" s="150"/>
+      <c r="AZ15" s="150"/>
+      <c r="BA15" s="151"/>
+      <c r="BB15" s="149">
         <v>46295</v>
       </c>
-      <c r="BC15" s="142" t="s">
+      <c r="BC15" s="150" t="s">
         <v>28</v>
       </c>
-      <c r="BD15" s="142"/>
-      <c r="BE15" s="142"/>
-      <c r="BF15" s="143"/>
-      <c r="BG15" s="141">
+      <c r="BD15" s="150"/>
+      <c r="BE15" s="150"/>
+      <c r="BF15" s="151"/>
+      <c r="BG15" s="149">
         <v>46326</v>
       </c>
-      <c r="BH15" s="142" t="s">
+      <c r="BH15" s="150" t="s">
         <v>29</v>
       </c>
-      <c r="BI15" s="142"/>
-      <c r="BJ15" s="142"/>
-      <c r="BK15" s="143"/>
-      <c r="BL15" s="141">
+      <c r="BI15" s="150"/>
+      <c r="BJ15" s="150"/>
+      <c r="BK15" s="151"/>
+      <c r="BL15" s="149">
         <v>46356</v>
       </c>
-      <c r="BM15" s="142" t="s">
+      <c r="BM15" s="150" t="s">
         <v>30</v>
       </c>
-      <c r="BN15" s="142"/>
-      <c r="BO15" s="142"/>
-      <c r="BP15" s="143"/>
-      <c r="BQ15" s="141">
+      <c r="BN15" s="150"/>
+      <c r="BO15" s="150"/>
+      <c r="BP15" s="151"/>
+      <c r="BQ15" s="149">
         <v>46387</v>
       </c>
-      <c r="BR15" s="142" t="s">
+      <c r="BR15" s="150" t="s">
         <v>31</v>
       </c>
-      <c r="BS15" s="142"/>
-      <c r="BT15" s="142"/>
-      <c r="BU15" s="143"/>
+      <c r="BS15" s="150"/>
+      <c r="BT15" s="150"/>
+      <c r="BU15" s="151"/>
       <c r="BV15" s="19">
         <f>SUM(BV17:BV65)</f>
         <v>7934948.8299999991</v>
@@ -8798,6 +8798,30 @@
   </sheetData>
   <autoFilter ref="A16:DD71" xr:uid="{177F1DEB-197D-49C6-A2E3-152C1AC7B373}"/>
   <mergeCells count="40">
+    <mergeCell ref="BQ13:BU13"/>
+    <mergeCell ref="BQ15:BU15"/>
+    <mergeCell ref="S13:W13"/>
+    <mergeCell ref="N13:R13"/>
+    <mergeCell ref="X13:AB13"/>
+    <mergeCell ref="AC13:AG13"/>
+    <mergeCell ref="AH13:AL13"/>
+    <mergeCell ref="AM13:AQ13"/>
+    <mergeCell ref="AR13:AV13"/>
+    <mergeCell ref="AW13:BA13"/>
+    <mergeCell ref="BB13:BF13"/>
+    <mergeCell ref="BG13:BK13"/>
+    <mergeCell ref="BL13:BP13"/>
+    <mergeCell ref="S15:W15"/>
+    <mergeCell ref="N15:R15"/>
+    <mergeCell ref="X15:AB15"/>
+    <mergeCell ref="BB14:BF14"/>
+    <mergeCell ref="BG14:BK14"/>
+    <mergeCell ref="BL14:BP14"/>
+    <mergeCell ref="AC15:AG15"/>
+    <mergeCell ref="AH15:AL15"/>
+    <mergeCell ref="AM15:AQ15"/>
+    <mergeCell ref="AR15:AV15"/>
+    <mergeCell ref="AW15:BA15"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="BQ14:BU14"/>
     <mergeCell ref="L13:M13"/>
@@ -8814,30 +8838,6 @@
     <mergeCell ref="AM14:AQ14"/>
     <mergeCell ref="AR14:AV14"/>
     <mergeCell ref="AW14:BA14"/>
-    <mergeCell ref="BB14:BF14"/>
-    <mergeCell ref="BG14:BK14"/>
-    <mergeCell ref="BL14:BP14"/>
-    <mergeCell ref="AC15:AG15"/>
-    <mergeCell ref="AH15:AL15"/>
-    <mergeCell ref="AM15:AQ15"/>
-    <mergeCell ref="AR15:AV15"/>
-    <mergeCell ref="AW15:BA15"/>
-    <mergeCell ref="BQ13:BU13"/>
-    <mergeCell ref="BQ15:BU15"/>
-    <mergeCell ref="S13:W13"/>
-    <mergeCell ref="N13:R13"/>
-    <mergeCell ref="X13:AB13"/>
-    <mergeCell ref="AC13:AG13"/>
-    <mergeCell ref="AH13:AL13"/>
-    <mergeCell ref="AM13:AQ13"/>
-    <mergeCell ref="AR13:AV13"/>
-    <mergeCell ref="AW13:BA13"/>
-    <mergeCell ref="BB13:BF13"/>
-    <mergeCell ref="BG13:BK13"/>
-    <mergeCell ref="BL13:BP13"/>
-    <mergeCell ref="S15:W15"/>
-    <mergeCell ref="N15:R15"/>
-    <mergeCell ref="X15:AB15"/>
   </mergeCells>
   <conditionalFormatting sqref="Q17:Q65 V17:V65 AA17:AA65 AF17:AF65 AK17:AK65 AP17:AP65 AU17:AU65 AZ17:AZ65 BE17:BE65 BJ17:BJ65 BO17:BO65 BT17:BT65">
     <cfRule type="expression" dxfId="3" priority="8">
@@ -9029,18 +9029,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9062,14 +9062,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3614A8F8-9AED-4C02-B640-81A3A1FEB080}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BC2B212-31BA-49FB-B215-9E14B2C60948}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -9083,4 +9075,12 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3614A8F8-9AED-4C02-B640-81A3A1FEB080}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/templates/Ram 2026_Owen Testing.xlsx
+++ b/data/templates/Ram 2026_Owen Testing.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pfizer-my.sharepoint.com/personal/hoveyo_pfizer_com/Documents/financial-automation-project/data/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A1710ED-9570-4990-9C3D-DDE87217A9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{7A1710ED-9570-4990-9C3D-DDE87217A9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89BC7557-4DC5-4339-B664-F1819F265931}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12480" tabRatio="590" xr2:uid="{0996C49B-04E6-42AE-AA83-2F64BE89A626}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Template!$A$16:$DD$16</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -76,7 +76,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q17" authorId="0" shapeId="0" xr:uid="{8E792CC1-515E-4E8D-AF02-12F449ADC8BA}">
+    <comment ref="Q17" authorId="0" shapeId="0" xr:uid="{DA9C12AB-FC72-4A52-B208-7A3C98427FAC}">
       <text>
         <r>
           <rPr>
@@ -121,7 +121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q18" authorId="0" shapeId="0" xr:uid="{A70132EB-F713-4D83-A235-68E2CF828BAA}">
+    <comment ref="Q18" authorId="0" shapeId="0" xr:uid="{F3F458D8-53E1-4CB4-9954-BB8122B7FCDB}">
       <text>
         <r>
           <rPr>
@@ -227,7 +227,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q48" authorId="0" shapeId="0" xr:uid="{14DBEB6D-8966-46B7-97FB-A2E7C508BC5F}">
+    <comment ref="Q48" authorId="0" shapeId="0" xr:uid="{690DC7AD-0D20-4513-B8FD-989347A0B119}">
       <text>
         <r>
           <rPr>
@@ -272,7 +272,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q49" authorId="0" shapeId="0" xr:uid="{CE13113B-30C4-47B2-9DFA-97539F866146}">
+    <comment ref="Q49" authorId="0" shapeId="0" xr:uid="{FA4AB58A-AF73-4B91-AE65-4BB99CCCEE10}">
       <text>
         <r>
           <rPr>
@@ -302,7 +302,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q52" authorId="0" shapeId="0" xr:uid="{3B120D52-DC11-43D5-9C64-C92AFB40679E}">
+    <comment ref="Q52" authorId="0" shapeId="0" xr:uid="{E580CE16-B6C3-4BBE-9459-EF58FA265326}">
       <text>
         <r>
           <rPr>
@@ -363,7 +363,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q62" authorId="0" shapeId="0" xr:uid="{050A5BCF-8FF8-4FC3-9183-26CC7C8394EE}">
+    <comment ref="Q62" authorId="0" shapeId="0" xr:uid="{76A96AA7-3E95-49AE-BE1F-C6CCD229EEC9}">
       <text>
         <r>
           <rPr>
@@ -393,7 +393,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q63" authorId="0" shapeId="0" xr:uid="{1633236B-5553-4763-A887-34F8F244926E}">
+    <comment ref="Q63" authorId="0" shapeId="0" xr:uid="{2592184C-148B-4DFF-A505-08DC1F439B21}">
       <text>
         <r>
           <rPr>
@@ -2341,7 +2341,14 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2 2" xfId="3" xr:uid="{EFDA3BDD-7E2C-4F3B-BEB7-091BB23895D4}"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3058,7 +3065,7 @@
       <c r="M13" s="144"/>
       <c r="N13" s="140" cm="1">
         <f t="array" ref="N13">SUM(Q17:Q65)+SUM(_xlfn._xlws.FILTER(P17:P65,Q17:Q65=""))+SUM(_xlfn._xlws.FILTER(O17:O65,(P17:P65="")*(Q17:Q65="")))+SUMIFS(R17:R65,Q17:Q65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(N17:N65)</f>
-        <v>685594.25000000012</v>
+        <v>410369.37000000011</v>
       </c>
       <c r="O13" s="141"/>
       <c r="P13" s="141"/>
@@ -3066,7 +3073,7 @@
       <c r="R13" s="142"/>
       <c r="S13" s="140" cm="1">
         <f t="array" ref="S13">SUM(V17:V65)+SUM(_xlfn._xlws.FILTER(U17:U65,V17:V65=""))+SUM(_xlfn._xlws.FILTER(T17:T65,(U17:U65="")*(V17:V65="")))+SUMIFS(W17:W65,V17:V65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(S17:S65)</f>
-        <v>891985.88</v>
+        <v>0</v>
       </c>
       <c r="T13" s="141"/>
       <c r="U13" s="141"/>
@@ -3074,7 +3081,7 @@
       <c r="W13" s="142"/>
       <c r="X13" s="140" cm="1">
         <f t="array" ref="X13">SUM(AA17:AA65)+SUM(_xlfn._xlws.FILTER(Z17:Z65,AA17:AA65=""))+SUM(_xlfn._xlws.FILTER(Y17:Y65,(Z17:Z65="")*(AA17:AA65="")))+SUMIFS(AB17:AB65,AA17:AA65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(X17:X65)</f>
-        <v>647579.66999999993</v>
+        <v>0</v>
       </c>
       <c r="Y13" s="141"/>
       <c r="Z13" s="141"/>
@@ -3082,7 +3089,7 @@
       <c r="AB13" s="142"/>
       <c r="AC13" s="140" cm="1">
         <f t="array" ref="AC13">SUM(AF17:AF65)+SUM(_xlfn._xlws.FILTER(AE17:AE65,AF17:AF65=""))+SUM(_xlfn._xlws.FILTER(AD17:AD65,(AE17:AE65="")*(AF17:AF65="")))+SUMIFS(AG17:AG65,AF17:AF65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(AC17:AC65)</f>
-        <v>647579.66999999993</v>
+        <v>0</v>
       </c>
       <c r="AD13" s="141"/>
       <c r="AE13" s="141"/>
@@ -3090,7 +3097,7 @@
       <c r="AG13" s="142"/>
       <c r="AH13" s="140" cm="1">
         <f t="array" ref="AH13">SUM(AK17:AK65)+SUM(_xlfn._xlws.FILTER(AJ17:AJ65,AK17:AK65=""))+SUM(_xlfn._xlws.FILTER(AI17:AI65,(AJ17:AJ65="")*(AK17:AK65="")))+SUMIFS(AL17:AL65,AK17:AK65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(AH17:AH65)</f>
-        <v>645269.66999999993</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="141"/>
       <c r="AJ13" s="141"/>
@@ -3098,7 +3105,7 @@
       <c r="AL13" s="142"/>
       <c r="AM13" s="140" cm="1">
         <f t="array" ref="AM13">SUM(AP17:AP65)+SUM(_xlfn._xlws.FILTER(AO17:AO65,AP17:AP65=""))+SUM(_xlfn._xlws.FILTER(AN17:AN65,(AO17:AO65="")*(AP17:AP65="")))+SUMIFS(AQ17:AQ65,AP17:AP65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(AM17:AM65)</f>
-        <v>635449.66999999993</v>
+        <v>0</v>
       </c>
       <c r="AN13" s="141"/>
       <c r="AO13" s="141"/>
@@ -3106,7 +3113,7 @@
       <c r="AQ13" s="142"/>
       <c r="AR13" s="140" cm="1">
         <f t="array" ref="AR13">SUM(AU17:AU65)+SUM(_xlfn._xlws.FILTER(AT17:AT65,AU17:AU65=""))+SUM(_xlfn._xlws.FILTER(AS17:AS65,(AT17:AT65="")*(AU17:AU65="")))+SUMIFS(AV17:AV65,AU17:AU65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(AR17:AR65)</f>
-        <v>635449.66999999993</v>
+        <v>0</v>
       </c>
       <c r="AS13" s="141"/>
       <c r="AT13" s="141"/>
@@ -3114,7 +3121,7 @@
       <c r="AV13" s="142"/>
       <c r="AW13" s="140" cm="1">
         <f t="array" ref="AW13">SUM(AZ17:AZ65)+SUM(_xlfn._xlws.FILTER(AY17:AY65,AZ17:AZ65=""))+SUM(_xlfn._xlws.FILTER(AX17:AX65,(AY17:AY65="")*(AZ17:AZ65="")))+SUMIFS(BA17:BA65,AZ17:AZ65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(AW17:AW65)</f>
-        <v>635449.66999999993</v>
+        <v>0</v>
       </c>
       <c r="AX13" s="141"/>
       <c r="AY13" s="141"/>
@@ -3122,7 +3129,7 @@
       <c r="BA13" s="142"/>
       <c r="BB13" s="140" cm="1">
         <f t="array" ref="BB13">SUM(BE17:BE65)+SUM(_xlfn._xlws.FILTER(BD17:BD65,BE17:BE65=""))+SUM(_xlfn._xlws.FILTER(BC17:BC65,(BD17:BD65="")*(BE17:BE65="")))+SUMIFS(BF17:BF65,BE17:BE65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(BB17:BB65)</f>
-        <v>635449.66999999993</v>
+        <v>0</v>
       </c>
       <c r="BC13" s="141"/>
       <c r="BD13" s="141"/>
@@ -3130,7 +3137,7 @@
       <c r="BF13" s="142"/>
       <c r="BG13" s="140" cm="1">
         <f t="array" ref="BG13">SUM(BJ17:BJ65)+SUM(_xlfn._xlws.FILTER(BI17:BI65,BJ17:BJ65=""))+SUM(_xlfn._xlws.FILTER(BH17:BH65,(BI17:BI65="")*(BJ17:BJ65="")))+SUMIFS(BK17:BK65,BJ17:BJ65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(BG17:BG65)</f>
-        <v>635449.66999999993</v>
+        <v>0</v>
       </c>
       <c r="BH13" s="141"/>
       <c r="BI13" s="141"/>
@@ -3138,7 +3145,7 @@
       <c r="BK13" s="142"/>
       <c r="BL13" s="140" cm="1">
         <f t="array" ref="BL13">SUM(BO17:BO65)+SUM(_xlfn._xlws.FILTER(BN17:BN65,BO17:BO65=""))+SUM(_xlfn._xlws.FILTER(BM17:BM65,(BN17:BN65="")*(BO17:BO65="")))+SUMIFS(BP17:BP65,BO17:BO65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(BL17:BL65)</f>
-        <v>635449.66999999993</v>
+        <v>0</v>
       </c>
       <c r="BM13" s="141"/>
       <c r="BN13" s="141"/>
@@ -3146,7 +3153,7 @@
       <c r="BP13" s="142"/>
       <c r="BQ13" s="140" cm="1">
         <f t="array" ref="BQ13">SUM(BT17:BT65)+SUM(_xlfn._xlws.FILTER(BS17:BS65,BT17:BT65=""))+SUM(_xlfn._xlws.FILTER(BR17:BR65,(BS17:BS65="")*(BT17:BT65="")))+SUMIFS(BU17:BU65,BT17:BT65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(BQ17:BQ65)</f>
-        <v>635449.66999999993</v>
+        <v>0</v>
       </c>
       <c r="BR13" s="141"/>
       <c r="BS13" s="141"/>
@@ -3157,7 +3164,7 @@
       </c>
       <c r="BW13" s="17">
         <f>BW15-BV15</f>
-        <v>-7934948.8299999991</v>
+        <v>-556862.20000000007</v>
       </c>
     </row>
     <row r="14" spans="1:77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3179,7 +3186,7 @@
       <c r="M14" s="146"/>
       <c r="N14" s="140" cm="1">
         <f t="array" ref="N14">SUM(Q17:Q65)+SUM(_xlfn._xlws.FILTER(P17:P65,Q17:Q65=""))+SUM(_xlfn._xlws.FILTER(O17:O65,(P17:P65="")*(Q17:Q65="")))</f>
-        <v>674619.25000000012</v>
+        <v>556862.20000000007</v>
       </c>
       <c r="O14" s="141"/>
       <c r="P14" s="141"/>
@@ -3187,7 +3194,7 @@
       <c r="R14" s="142"/>
       <c r="S14" s="140" cm="1">
         <f t="array" ref="S14">SUM(V17:V65)+SUM(_xlfn._xlws.FILTER(U17:U65,V17:V65=""))+SUM(_xlfn._xlws.FILTER(T17:T65,(U17:U65="")*(V17:V65="")))</f>
-        <v>871752.88</v>
+        <v>0</v>
       </c>
       <c r="T14" s="141"/>
       <c r="U14" s="141"/>
@@ -3195,7 +3202,7 @@
       <c r="W14" s="142"/>
       <c r="X14" s="140" cm="1">
         <f t="array" ref="X14">SUM(AA17:AA65)+SUM(_xlfn._xlws.FILTER(Z17:Z65,AA17:AA65=""))+SUM(_xlfn._xlws.FILTER(Y17:Y65,(Z17:Z65="")*(AA17:AA65="")))</f>
-        <v>647579.66999999993</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="141"/>
       <c r="Z14" s="141"/>
@@ -3203,7 +3210,7 @@
       <c r="AB14" s="142"/>
       <c r="AC14" s="140" cm="1">
         <f t="array" ref="AC14">SUM(AF17:AF65)+SUM(_xlfn._xlws.FILTER(AE17:AE65,AF17:AF65=""))+SUM(_xlfn._xlws.FILTER(AD17:AD65,(AE17:AE65="")*(AF17:AF65="")))</f>
-        <v>647579.66999999993</v>
+        <v>0</v>
       </c>
       <c r="AD14" s="141"/>
       <c r="AE14" s="141"/>
@@ -3211,7 +3218,7 @@
       <c r="AG14" s="142"/>
       <c r="AH14" s="140" cm="1">
         <f t="array" ref="AH14">SUM(AK17:AK65)+SUM(_xlfn._xlws.FILTER(AJ17:AJ65,AK17:AK65=""))+SUM(_xlfn._xlws.FILTER(AI17:AI65,(AJ17:AJ65="")*(AK17:AK65="")))</f>
-        <v>645269.66999999993</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="141"/>
       <c r="AJ14" s="141"/>
@@ -3219,7 +3226,7 @@
       <c r="AL14" s="142"/>
       <c r="AM14" s="140" cm="1">
         <f t="array" ref="AM14">SUM(AP17:AP65)+SUM(_xlfn._xlws.FILTER(AO17:AO65,AP17:AP65=""))+SUM(_xlfn._xlws.FILTER(AN17:AN65,(AO17:AO65="")*(AP17:AP65="")))</f>
-        <v>635449.66999999993</v>
+        <v>0</v>
       </c>
       <c r="AN14" s="141"/>
       <c r="AO14" s="141"/>
@@ -3227,7 +3234,7 @@
       <c r="AQ14" s="142"/>
       <c r="AR14" s="140" cm="1">
         <f t="array" ref="AR14">SUM(AU17:AU65)+SUM(_xlfn._xlws.FILTER(AT17:AT65,AU17:AU65=""))+SUM(_xlfn._xlws.FILTER(AS17:AS65,(AT17:AT65="")*(AU17:AU65="")))</f>
-        <v>635449.66999999993</v>
+        <v>0</v>
       </c>
       <c r="AS14" s="141"/>
       <c r="AT14" s="141"/>
@@ -3235,7 +3242,7 @@
       <c r="AV14" s="142"/>
       <c r="AW14" s="140" cm="1">
         <f t="array" ref="AW14">SUM(AZ17:AZ65)+SUM(_xlfn._xlws.FILTER(AY17:AY65,AZ17:AZ65=""))+SUM(_xlfn._xlws.FILTER(AX17:AX65,(AY17:AY65="")*(AZ17:AZ65="")))</f>
-        <v>635449.66999999993</v>
+        <v>0</v>
       </c>
       <c r="AX14" s="141"/>
       <c r="AY14" s="141"/>
@@ -3243,7 +3250,7 @@
       <c r="BA14" s="142"/>
       <c r="BB14" s="140" cm="1">
         <f t="array" ref="BB14">SUM(BE17:BE65)+SUM(_xlfn._xlws.FILTER(BD17:BD65,BE17:BE65=""))+SUM(_xlfn._xlws.FILTER(BC17:BC65,(BD17:BD65="")*(BE17:BE65="")))</f>
-        <v>635449.66999999993</v>
+        <v>0</v>
       </c>
       <c r="BC14" s="141"/>
       <c r="BD14" s="141"/>
@@ -3251,7 +3258,7 @@
       <c r="BF14" s="142"/>
       <c r="BG14" s="140" cm="1">
         <f t="array" ref="BG14">SUM(BJ17:BJ65)+SUM(_xlfn._xlws.FILTER(BI17:BI65,BJ17:BJ65=""))+SUM(_xlfn._xlws.FILTER(BH17:BH65,(BI17:BI65="")*(BJ17:BJ65="")))</f>
-        <v>635449.66999999993</v>
+        <v>0</v>
       </c>
       <c r="BH14" s="141"/>
       <c r="BI14" s="141"/>
@@ -3259,7 +3266,7 @@
       <c r="BK14" s="142"/>
       <c r="BL14" s="140" cm="1">
         <f t="array" ref="BL14">SUM(BO17:BO65)+SUM(_xlfn._xlws.FILTER(BN17:BN65,BO17:BO65=""))+SUM(_xlfn._xlws.FILTER(BM17:BM65,(BN17:BN65="")*(BO17:BO65="")))</f>
-        <v>635449.66999999993</v>
+        <v>0</v>
       </c>
       <c r="BM14" s="141"/>
       <c r="BN14" s="141"/>
@@ -3267,7 +3274,7 @@
       <c r="BP14" s="142"/>
       <c r="BQ14" s="140" cm="1">
         <f t="array" ref="BQ14">SUM(BT17:BT65)+SUM(_xlfn._xlws.FILTER(BS17:BS65,BT17:BT65=""))+SUM(_xlfn._xlws.FILTER(BR17:BR65,(BS17:BS65="")*(BT17:BT65="")))</f>
-        <v>635449.66999999993</v>
+        <v>0</v>
       </c>
       <c r="BR14" s="141"/>
       <c r="BS14" s="141"/>
@@ -3396,7 +3403,7 @@
       <c r="BU15" s="151"/>
       <c r="BV15" s="19">
         <f>SUM(BV17:BV65)</f>
-        <v>7934948.8299999991</v>
+        <v>556862.20000000007</v>
       </c>
       <c r="BW15" s="20"/>
       <c r="BY15" s="15"/>
@@ -3671,121 +3678,77 @@
       <c r="M17" s="99" t="s">
         <v>102</v>
       </c>
-      <c r="N17" s="91"/>
+      <c r="N17" s="91">
+        <v>0</v>
+      </c>
       <c r="O17" s="34">
         <v>10975</v>
       </c>
-      <c r="P17" s="34"/>
+      <c r="P17" s="34">
+        <v>11347.01</v>
+      </c>
       <c r="Q17" s="82">
-        <v>10125.75</v>
-      </c>
-      <c r="R17" s="36">
-        <f>P17-Q17</f>
-        <v>-10125.75</v>
-      </c>
+        <v>10656.33</v>
+      </c>
+      <c r="R17" s="36"/>
       <c r="S17" s="35"/>
-      <c r="T17" s="34">
-        <v>10398</v>
-      </c>
-      <c r="U17" s="34">
-        <v>9776.5499999999993</v>
-      </c>
-      <c r="V17" s="82">
-        <v>10888</v>
-      </c>
-      <c r="W17" s="37">
-        <f t="shared" ref="W17:W64" si="0">U17-V17</f>
-        <v>-1111.4500000000007</v>
-      </c>
+      <c r="T17" s="34"/>
+      <c r="U17" s="34"/>
+      <c r="V17" s="82"/>
+      <c r="W17" s="37"/>
       <c r="X17" s="38"/>
-      <c r="Y17" s="34">
-        <v>12130</v>
-      </c>
+      <c r="Y17" s="34"/>
       <c r="Z17" s="34"/>
       <c r="AA17" s="36"/>
-      <c r="AB17" s="42">
-        <f>Z17-AA17</f>
-        <v>0</v>
-      </c>
+      <c r="AB17" s="42"/>
       <c r="AC17" s="38"/>
-      <c r="AD17" s="34">
-        <v>12130</v>
-      </c>
+      <c r="AD17" s="34"/>
       <c r="AE17" s="34"/>
       <c r="AF17" s="36"/>
-      <c r="AG17" s="42">
-        <f>AE17-AF17</f>
-        <v>0</v>
-      </c>
+      <c r="AG17" s="42"/>
       <c r="AH17" s="38"/>
-      <c r="AI17" s="34">
-        <v>9820</v>
-      </c>
+      <c r="AI17" s="34"/>
       <c r="AJ17" s="34"/>
       <c r="AK17" s="36"/>
-      <c r="AL17" s="42">
-        <f>AJ17-AK17</f>
-        <v>0</v>
-      </c>
+      <c r="AL17" s="42"/>
       <c r="AM17" s="38"/>
       <c r="AN17" s="34"/>
       <c r="AO17" s="34"/>
       <c r="AP17" s="36"/>
-      <c r="AQ17" s="42">
-        <f>AO17-AP17</f>
-        <v>0</v>
-      </c>
+      <c r="AQ17" s="42"/>
       <c r="AR17" s="38"/>
       <c r="AS17" s="34"/>
       <c r="AT17" s="34"/>
       <c r="AU17" s="36"/>
-      <c r="AV17" s="42">
-        <f>AT17-AU17</f>
-        <v>0</v>
-      </c>
+      <c r="AV17" s="42"/>
       <c r="AW17" s="38"/>
       <c r="AX17" s="34"/>
       <c r="AY17" s="34"/>
       <c r="AZ17" s="36"/>
-      <c r="BA17" s="42">
-        <f>AY17-AZ17</f>
-        <v>0</v>
-      </c>
+      <c r="BA17" s="42"/>
       <c r="BB17" s="38"/>
       <c r="BC17" s="34"/>
       <c r="BD17" s="34"/>
       <c r="BE17" s="36"/>
-      <c r="BF17" s="42">
-        <f>BD17-BE17</f>
-        <v>0</v>
-      </c>
+      <c r="BF17" s="42"/>
       <c r="BG17" s="38"/>
       <c r="BH17" s="34"/>
       <c r="BI17" s="34"/>
       <c r="BJ17" s="36"/>
-      <c r="BK17" s="42">
-        <f>BI17-BJ17</f>
-        <v>0</v>
-      </c>
+      <c r="BK17" s="42"/>
       <c r="BL17" s="38"/>
       <c r="BM17" s="34"/>
       <c r="BN17" s="34"/>
       <c r="BO17" s="36"/>
-      <c r="BP17" s="42">
-        <f>BN17-BO17</f>
-        <v>0</v>
-      </c>
+      <c r="BP17" s="42"/>
       <c r="BQ17" s="38"/>
       <c r="BR17" s="34"/>
       <c r="BS17" s="34"/>
       <c r="BT17" s="36"/>
-      <c r="BU17" s="42">
-        <f t="shared" ref="BU17:BU64" si="1">BS17-BT17</f>
-        <v>0</v>
-      </c>
+      <c r="BU17" s="42"/>
       <c r="BV17" s="35">
-        <f t="shared" ref="BV17:BV65" si="2">SUM(IF(Q17&lt;&gt;"",Q17,IF(P17&lt;&gt;"",P17,O17)),IF(V17&lt;&gt;"",V17,IF(U17&lt;&gt;"",U17,T17)),IF(AA17&lt;&gt;"",AA17,IF(Z17&lt;&gt;"",Z17,Y17)),IF(AF17&lt;&gt;"",AF17,IF(AE17&lt;&gt;"",AE17,AD17)),IF(AK17&lt;&gt;"",AK17,IF(AJ17&lt;&gt;"",AJ17,AI17)),IF(AP17&lt;&gt;"",AP17,IF(AO17&lt;&gt;"",AO17,AN17)),IF(AU17&lt;&gt;"",AU17,IF(AT17&lt;&gt;"",AT17,AS17)),IF(AZ17&lt;&gt;"",AZ17,IF(AY17&lt;&gt;"",AY17,AX17)),IF(BE17&lt;&gt;"",BE17,IF(BD17&lt;&gt;"",BD17,BC17)),IF(BJ17&lt;&gt;"",BJ17,IF(BI17&lt;&gt;"",BI17,BH17)),IF(BO17&lt;&gt;"",BO17,IF(BN17&lt;&gt;"",BN17,BM17)),IF(BT17&lt;&gt;"",BT17,IF(BS17&lt;&gt;"",BS17,BR17)))</f>
-        <v>55093.75</v>
+        <f t="shared" ref="BV17:BV65" si="0">SUM(IF(Q17&lt;&gt;"",Q17,IF(P17&lt;&gt;"",P17,O17)),IF(V17&lt;&gt;"",V17,IF(U17&lt;&gt;"",U17,T17)),IF(AA17&lt;&gt;"",AA17,IF(Z17&lt;&gt;"",Z17,Y17)),IF(AF17&lt;&gt;"",AF17,IF(AE17&lt;&gt;"",AE17,AD17)),IF(AK17&lt;&gt;"",AK17,IF(AJ17&lt;&gt;"",AJ17,AI17)),IF(AP17&lt;&gt;"",AP17,IF(AO17&lt;&gt;"",AO17,AN17)),IF(AU17&lt;&gt;"",AU17,IF(AT17&lt;&gt;"",AT17,AS17)),IF(AZ17&lt;&gt;"",AZ17,IF(AY17&lt;&gt;"",AY17,AX17)),IF(BE17&lt;&gt;"",BE17,IF(BD17&lt;&gt;"",BD17,BC17)),IF(BJ17&lt;&gt;"",BJ17,IF(BI17&lt;&gt;"",BI17,BH17)),IF(BO17&lt;&gt;"",BO17,IF(BN17&lt;&gt;"",BN17,BM17)),IF(BT17&lt;&gt;"",BT17,IF(BS17&lt;&gt;"",BS17,BR17)))</f>
+        <v>10656.33</v>
       </c>
       <c r="BW17" s="49"/>
       <c r="BX17" s="50"/>
@@ -3830,109 +3793,77 @@
       <c r="M18" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="N18" s="92"/>
-      <c r="O18" s="39"/>
-      <c r="P18" s="39"/>
+      <c r="N18" s="92">
+        <v>0</v>
+      </c>
+      <c r="O18" s="39">
+        <v>10296</v>
+      </c>
+      <c r="P18" s="39">
+        <v>10548.89</v>
+      </c>
       <c r="Q18" s="85">
-        <v>10296</v>
-      </c>
-      <c r="R18" s="41">
-        <f t="shared" ref="R18:R64" si="3">P18-Q18</f>
-        <v>-10296</v>
-      </c>
+        <v>10636.8</v>
+      </c>
+      <c r="R18" s="41"/>
       <c r="S18" s="40"/>
       <c r="T18" s="39"/>
       <c r="U18" s="39"/>
-      <c r="V18" s="85">
-        <v>10296</v>
-      </c>
-      <c r="W18" s="42">
-        <f t="shared" si="0"/>
-        <v>-10296</v>
-      </c>
+      <c r="V18" s="85"/>
+      <c r="W18" s="42"/>
       <c r="X18" s="43"/>
       <c r="Y18" s="39"/>
       <c r="Z18" s="39"/>
       <c r="AA18" s="41"/>
-      <c r="AB18" s="42">
-        <f t="shared" ref="AB18:AB64" si="4">Z18-AA18</f>
-        <v>0</v>
-      </c>
+      <c r="AB18" s="42"/>
       <c r="AC18" s="43"/>
       <c r="AD18" s="39"/>
       <c r="AE18" s="39"/>
       <c r="AF18" s="39"/>
-      <c r="AG18" s="42">
-        <f t="shared" ref="AG18:AG64" si="5">AE18-AF18</f>
-        <v>0</v>
-      </c>
+      <c r="AG18" s="42"/>
       <c r="AH18" s="43"/>
       <c r="AI18" s="39"/>
       <c r="AJ18" s="39"/>
       <c r="AK18" s="39"/>
-      <c r="AL18" s="42">
-        <f t="shared" ref="AL18:AL64" si="6">AJ18-AK18</f>
-        <v>0</v>
-      </c>
+      <c r="AL18" s="42"/>
       <c r="AM18" s="43"/>
       <c r="AN18" s="39"/>
       <c r="AO18" s="39"/>
       <c r="AP18" s="39"/>
-      <c r="AQ18" s="42">
-        <f t="shared" ref="AQ18:AQ64" si="7">AO18-AP18</f>
-        <v>0</v>
-      </c>
+      <c r="AQ18" s="42"/>
       <c r="AR18" s="43"/>
       <c r="AS18" s="39"/>
       <c r="AT18" s="39"/>
       <c r="AU18" s="39"/>
-      <c r="AV18" s="42">
-        <f t="shared" ref="AV18:AV64" si="8">AT18-AU18</f>
-        <v>0</v>
-      </c>
+      <c r="AV18" s="42"/>
       <c r="AW18" s="43"/>
       <c r="AX18" s="39"/>
       <c r="AY18" s="39"/>
       <c r="AZ18" s="39"/>
-      <c r="BA18" s="42">
-        <f t="shared" ref="BA18:BA64" si="9">AY18-AZ18</f>
-        <v>0</v>
-      </c>
+      <c r="BA18" s="42"/>
       <c r="BB18" s="43"/>
       <c r="BC18" s="39"/>
       <c r="BD18" s="39"/>
       <c r="BE18" s="39"/>
-      <c r="BF18" s="42">
-        <f t="shared" ref="BF18:BF64" si="10">BD18-BE18</f>
-        <v>0</v>
-      </c>
+      <c r="BF18" s="42"/>
       <c r="BG18" s="43"/>
       <c r="BH18" s="39"/>
       <c r="BI18" s="39"/>
       <c r="BJ18" s="39"/>
-      <c r="BK18" s="42">
-        <f t="shared" ref="BK18:BK64" si="11">BI18-BJ18</f>
-        <v>0</v>
-      </c>
+      <c r="BK18" s="42"/>
       <c r="BL18" s="43"/>
       <c r="BM18" s="39"/>
       <c r="BN18" s="39"/>
       <c r="BO18" s="39"/>
-      <c r="BP18" s="42">
-        <f t="shared" ref="BP18:BP64" si="12">BN18-BO18</f>
-        <v>0</v>
-      </c>
+      <c r="BP18" s="42"/>
       <c r="BQ18" s="43"/>
       <c r="BR18" s="39"/>
       <c r="BS18" s="39"/>
       <c r="BT18" s="39"/>
-      <c r="BU18" s="42">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="BU18" s="42"/>
       <c r="BV18" s="35">
-        <f t="shared" si="2"/>
-        <v>20592</v>
+        <f t="shared" si="0"/>
+        <v>10636.8</v>
       </c>
       <c r="BW18" s="51"/>
       <c r="BX18" s="52"/>
@@ -4038,7 +3969,7 @@
       <c r="BT19" s="46"/>
       <c r="BU19" s="42"/>
       <c r="BV19" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW19" s="51"/>
@@ -4172,10 +4103,18 @@
       <c r="M21" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="N21" s="93"/>
-      <c r="O21" s="45"/>
-      <c r="P21" s="45"/>
-      <c r="Q21" s="85"/>
+      <c r="N21" s="93">
+        <v>0</v>
+      </c>
+      <c r="O21" s="45">
+        <v>0</v>
+      </c>
+      <c r="P21" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="85">
+        <v>0</v>
+      </c>
       <c r="R21" s="41"/>
       <c r="S21" s="44"/>
       <c r="T21" s="39"/>
@@ -4319,7 +4258,7 @@
       <c r="BT22" s="46"/>
       <c r="BU22" s="42"/>
       <c r="BV22" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW22" s="51"/>
@@ -4498,7 +4437,7 @@
       <c r="BT24" s="46"/>
       <c r="BU24" s="42"/>
       <c r="BV24" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW24" s="51"/>
@@ -4583,7 +4522,7 @@
       <c r="BT25" s="46"/>
       <c r="BU25" s="42"/>
       <c r="BV25" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW25" s="51"/>
@@ -4668,7 +4607,7 @@
       <c r="BT26" s="46"/>
       <c r="BU26" s="42"/>
       <c r="BV26" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW26" s="51"/>
@@ -4753,7 +4692,7 @@
       <c r="BT27" s="46"/>
       <c r="BU27" s="42"/>
       <c r="BV27" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW27" s="51"/>
@@ -4838,7 +4777,7 @@
       <c r="BT28" s="46"/>
       <c r="BU28" s="42"/>
       <c r="BV28" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW28" s="51"/>
@@ -4923,7 +4862,7 @@
       <c r="BT29" s="46"/>
       <c r="BU29" s="42"/>
       <c r="BV29" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW29" s="51"/>
@@ -5008,7 +4947,7 @@
       <c r="BT30" s="46"/>
       <c r="BU30" s="42"/>
       <c r="BV30" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW30" s="51"/>
@@ -5093,7 +5032,7 @@
       <c r="BT31" s="46"/>
       <c r="BU31" s="42"/>
       <c r="BV31" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW31" s="51"/>
@@ -5178,7 +5117,7 @@
       <c r="BT32" s="46"/>
       <c r="BU32" s="42"/>
       <c r="BV32" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW32" s="51"/>
@@ -5263,7 +5202,7 @@
       <c r="BT33" s="46"/>
       <c r="BU33" s="42"/>
       <c r="BV33" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW33" s="51"/>
@@ -5348,7 +5287,7 @@
       <c r="BT34" s="46"/>
       <c r="BU34" s="42"/>
       <c r="BV34" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW34" s="51"/>
@@ -5433,7 +5372,7 @@
       <c r="BT35" s="46"/>
       <c r="BU35" s="42"/>
       <c r="BV35" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW35" s="51"/>
@@ -5518,7 +5457,7 @@
       <c r="BT36" s="46"/>
       <c r="BU36" s="42"/>
       <c r="BV36" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW36" s="51"/>
@@ -5603,7 +5542,7 @@
       <c r="BT37" s="46"/>
       <c r="BU37" s="42"/>
       <c r="BV37" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW37" s="51"/>
@@ -5688,7 +5627,7 @@
       <c r="BT38" s="46"/>
       <c r="BU38" s="42"/>
       <c r="BV38" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW38" s="51"/>
@@ -5773,7 +5712,7 @@
       <c r="BT39" s="46"/>
       <c r="BU39" s="42"/>
       <c r="BV39" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW39" s="51"/>
@@ -5858,7 +5797,7 @@
       <c r="BT40" s="46"/>
       <c r="BU40" s="42"/>
       <c r="BV40" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW40" s="51"/>
@@ -5943,7 +5882,7 @@
       <c r="BT41" s="46"/>
       <c r="BU41" s="42"/>
       <c r="BV41" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW41" s="51"/>
@@ -6028,7 +5967,7 @@
       <c r="BT42" s="46"/>
       <c r="BU42" s="42"/>
       <c r="BV42" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW42" s="51"/>
@@ -6113,7 +6052,7 @@
       <c r="BT43" s="46"/>
       <c r="BU43" s="42"/>
       <c r="BV43" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW43" s="51"/>
@@ -6200,7 +6139,7 @@
       <c r="BT44" s="46"/>
       <c r="BU44" s="42"/>
       <c r="BV44" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW44" s="51"/>
@@ -6287,7 +6226,7 @@
       <c r="BT45" s="46"/>
       <c r="BU45" s="42"/>
       <c r="BV45" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW45" s="51"/>
@@ -6372,7 +6311,7 @@
       <c r="BT46" s="46"/>
       <c r="BU46" s="42"/>
       <c r="BV46" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW46" s="51"/>
@@ -6457,7 +6396,7 @@
       <c r="BT47" s="46"/>
       <c r="BU47" s="42"/>
       <c r="BV47" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW47" s="51"/>
@@ -6503,97 +6442,77 @@
       <c r="M48" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="N48" s="93"/>
+      <c r="N48" s="93">
+        <v>0</v>
+      </c>
       <c r="O48" s="45">
         <v>3123</v>
       </c>
-      <c r="P48" s="45"/>
+      <c r="P48" s="45">
+        <v>3217.02</v>
+      </c>
       <c r="Q48" s="81">
-        <v>3113.83</v>
+        <v>0</v>
       </c>
       <c r="R48" s="41"/>
       <c r="S48" s="44"/>
-      <c r="T48" s="39">
-        <v>3123</v>
-      </c>
+      <c r="T48" s="39"/>
       <c r="U48" s="39"/>
-      <c r="V48" s="81">
-        <v>3114</v>
-      </c>
+      <c r="V48" s="81"/>
       <c r="W48" s="42"/>
       <c r="X48" s="43"/>
-      <c r="Y48" s="39">
-        <v>3123</v>
-      </c>
+      <c r="Y48" s="39"/>
       <c r="Z48" s="39"/>
       <c r="AA48" s="46"/>
       <c r="AB48" s="42"/>
       <c r="AC48" s="43"/>
-      <c r="AD48" s="45">
-        <v>3123</v>
-      </c>
+      <c r="AD48" s="45"/>
       <c r="AE48" s="45"/>
       <c r="AF48" s="46"/>
       <c r="AG48" s="42"/>
       <c r="AH48" s="43"/>
-      <c r="AI48" s="45">
-        <v>3123</v>
-      </c>
+      <c r="AI48" s="45"/>
       <c r="AJ48" s="45"/>
       <c r="AK48" s="46"/>
       <c r="AL48" s="42"/>
       <c r="AM48" s="43"/>
-      <c r="AN48" s="45">
-        <v>3123</v>
-      </c>
+      <c r="AN48" s="45"/>
       <c r="AO48" s="45"/>
       <c r="AP48" s="46"/>
       <c r="AQ48" s="42"/>
       <c r="AR48" s="43"/>
-      <c r="AS48" s="45">
-        <v>3123</v>
-      </c>
+      <c r="AS48" s="45"/>
       <c r="AT48" s="45"/>
       <c r="AU48" s="46"/>
       <c r="AV48" s="42"/>
       <c r="AW48" s="43"/>
-      <c r="AX48" s="45">
-        <v>3123</v>
-      </c>
+      <c r="AX48" s="45"/>
       <c r="AY48" s="45"/>
       <c r="AZ48" s="46"/>
       <c r="BA48" s="42"/>
       <c r="BB48" s="43"/>
-      <c r="BC48" s="45">
-        <v>3123</v>
-      </c>
+      <c r="BC48" s="45"/>
       <c r="BD48" s="45"/>
       <c r="BE48" s="46"/>
       <c r="BF48" s="42"/>
       <c r="BG48" s="43"/>
-      <c r="BH48" s="45">
-        <v>3123</v>
-      </c>
+      <c r="BH48" s="45"/>
       <c r="BI48" s="45"/>
       <c r="BJ48" s="46"/>
       <c r="BK48" s="42"/>
       <c r="BL48" s="43"/>
-      <c r="BM48" s="45">
-        <v>3123</v>
-      </c>
+      <c r="BM48" s="45"/>
       <c r="BN48" s="45"/>
       <c r="BO48" s="46"/>
       <c r="BP48" s="42"/>
       <c r="BQ48" s="43"/>
-      <c r="BR48" s="45">
-        <v>3123</v>
-      </c>
+      <c r="BR48" s="45"/>
       <c r="BS48" s="45"/>
       <c r="BT48" s="46"/>
       <c r="BU48" s="42"/>
       <c r="BV48" s="35">
-        <f t="shared" si="2"/>
-        <v>37457.83</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="BW48" s="51"/>
       <c r="BX48" s="52"/>
@@ -6638,19 +6557,23 @@
       <c r="M49" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="N49" s="93"/>
-      <c r="O49" s="45"/>
-      <c r="P49" s="45"/>
+      <c r="N49" s="93">
+        <v>0</v>
+      </c>
+      <c r="O49" s="45">
+        <v>965</v>
+      </c>
+      <c r="P49" s="45">
+        <v>844.81</v>
+      </c>
       <c r="Q49" s="81">
-        <v>965</v>
+        <v>821.58</v>
       </c>
       <c r="R49" s="41"/>
       <c r="S49" s="44"/>
       <c r="T49" s="39"/>
       <c r="U49" s="39"/>
-      <c r="V49" s="81">
-        <v>965</v>
-      </c>
+      <c r="V49" s="81"/>
       <c r="W49" s="42"/>
       <c r="X49" s="43"/>
       <c r="Y49" s="39"/>
@@ -6703,8 +6626,8 @@
       <c r="BT49" s="46"/>
       <c r="BU49" s="42"/>
       <c r="BV49" s="35">
-        <f t="shared" si="2"/>
-        <v>1930</v>
+        <f t="shared" si="0"/>
+        <v>821.58</v>
       </c>
       <c r="BW49" s="51"/>
       <c r="BX49" s="52"/>
@@ -6790,7 +6713,7 @@
       <c r="BT50" s="46"/>
       <c r="BU50" s="42"/>
       <c r="BV50" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW50" s="92"/>
@@ -6877,7 +6800,7 @@
       <c r="BT51" s="46"/>
       <c r="BU51" s="42"/>
       <c r="BV51" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW51" s="92"/>
@@ -6923,133 +6846,77 @@
       <c r="M52" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="N52" s="93"/>
+      <c r="N52" s="93">
+        <v>0</v>
+      </c>
       <c r="O52" s="45">
-        <v>387633</v>
-      </c>
-      <c r="P52" s="45"/>
+        <v>0</v>
+      </c>
+      <c r="P52" s="45">
+        <v>387633.34</v>
+      </c>
       <c r="Q52" s="81">
-        <v>387633</v>
-      </c>
-      <c r="R52" s="41">
-        <f t="shared" si="3"/>
-        <v>-387633</v>
-      </c>
+        <v>387633.33</v>
+      </c>
+      <c r="R52" s="41"/>
       <c r="S52" s="44"/>
-      <c r="T52" s="45">
-        <v>387633</v>
-      </c>
-      <c r="U52" s="129">
-        <v>387633</v>
-      </c>
+      <c r="T52" s="45"/>
+      <c r="U52" s="129"/>
       <c r="V52" s="41"/>
-      <c r="W52" s="42">
-        <f t="shared" si="0"/>
-        <v>387633</v>
-      </c>
+      <c r="W52" s="42"/>
       <c r="X52" s="43"/>
-      <c r="Y52" s="45">
-        <v>387633</v>
-      </c>
+      <c r="Y52" s="45"/>
       <c r="Z52" s="39"/>
       <c r="AA52" s="46"/>
-      <c r="AB52" s="42">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+      <c r="AB52" s="42"/>
       <c r="AC52" s="43"/>
-      <c r="AD52" s="45">
-        <v>387633</v>
-      </c>
+      <c r="AD52" s="45"/>
       <c r="AE52" s="45"/>
       <c r="AF52" s="46"/>
-      <c r="AG52" s="42">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="AG52" s="42"/>
       <c r="AH52" s="43"/>
-      <c r="AI52" s="45">
-        <v>387633</v>
-      </c>
+      <c r="AI52" s="45"/>
       <c r="AJ52" s="45"/>
       <c r="AK52" s="46"/>
-      <c r="AL52" s="42">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
+      <c r="AL52" s="42"/>
       <c r="AM52" s="43"/>
-      <c r="AN52" s="45">
-        <v>387633</v>
-      </c>
+      <c r="AN52" s="45"/>
       <c r="AO52" s="45"/>
       <c r="AP52" s="46"/>
-      <c r="AQ52" s="42">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
+      <c r="AQ52" s="42"/>
       <c r="AR52" s="43"/>
-      <c r="AS52" s="45">
-        <v>387633</v>
-      </c>
+      <c r="AS52" s="45"/>
       <c r="AT52" s="45"/>
       <c r="AU52" s="46"/>
-      <c r="AV52" s="42">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="AV52" s="42"/>
       <c r="AW52" s="43"/>
-      <c r="AX52" s="45">
-        <v>387633</v>
-      </c>
+      <c r="AX52" s="45"/>
       <c r="AY52" s="45"/>
       <c r="AZ52" s="46"/>
-      <c r="BA52" s="42">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="BA52" s="42"/>
       <c r="BB52" s="43"/>
-      <c r="BC52" s="45">
-        <v>387633</v>
-      </c>
+      <c r="BC52" s="45"/>
       <c r="BD52" s="45"/>
       <c r="BE52" s="46"/>
-      <c r="BF52" s="42">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
+      <c r="BF52" s="42"/>
       <c r="BG52" s="43"/>
-      <c r="BH52" s="45">
-        <v>387633</v>
-      </c>
+      <c r="BH52" s="45"/>
       <c r="BI52" s="45"/>
       <c r="BJ52" s="46"/>
-      <c r="BK52" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
+      <c r="BK52" s="42"/>
       <c r="BL52" s="43"/>
-      <c r="BM52" s="45">
-        <v>387633</v>
-      </c>
+      <c r="BM52" s="45"/>
       <c r="BN52" s="45"/>
       <c r="BO52" s="46"/>
-      <c r="BP52" s="42">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
+      <c r="BP52" s="42"/>
       <c r="BQ52" s="43"/>
-      <c r="BR52" s="45">
-        <v>387633</v>
-      </c>
+      <c r="BR52" s="45"/>
       <c r="BS52" s="45"/>
       <c r="BT52" s="46"/>
-      <c r="BU52" s="42">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="BU52" s="42"/>
       <c r="BV52" s="35">
-        <f t="shared" si="2"/>
-        <v>4651596</v>
+        <f t="shared" si="0"/>
+        <v>387633.33</v>
       </c>
       <c r="BW52" s="51"/>
       <c r="BX52" s="52"/>
@@ -7095,94 +6962,68 @@
         <v>102</v>
       </c>
       <c r="N53" s="93"/>
-      <c r="O53" s="128">
-        <v>4166.67</v>
-      </c>
+      <c r="O53" s="128"/>
       <c r="P53" s="45"/>
       <c r="Q53" s="41"/>
       <c r="R53" s="41"/>
       <c r="S53" s="44"/>
-      <c r="T53" s="128">
-        <v>4166.67</v>
-      </c>
-      <c r="U53" s="39">
-        <v>17270</v>
-      </c>
+      <c r="T53" s="128"/>
+      <c r="U53" s="39"/>
       <c r="V53" s="41"/>
       <c r="W53" s="42"/>
       <c r="X53" s="43"/>
-      <c r="Y53" s="128">
-        <v>4166.67</v>
-      </c>
+      <c r="Y53" s="128"/>
       <c r="Z53" s="39"/>
       <c r="AA53" s="46"/>
       <c r="AB53" s="42"/>
       <c r="AC53" s="43"/>
-      <c r="AD53" s="128">
-        <v>4166.67</v>
-      </c>
+      <c r="AD53" s="128"/>
       <c r="AE53" s="45"/>
       <c r="AF53" s="46"/>
       <c r="AG53" s="42"/>
       <c r="AH53" s="43"/>
-      <c r="AI53" s="128">
-        <v>4166.67</v>
-      </c>
+      <c r="AI53" s="128"/>
       <c r="AJ53" s="45"/>
       <c r="AK53" s="46"/>
       <c r="AL53" s="42"/>
       <c r="AM53" s="43"/>
-      <c r="AN53" s="128">
-        <v>4166.67</v>
-      </c>
+      <c r="AN53" s="128"/>
       <c r="AO53" s="45"/>
       <c r="AP53" s="46"/>
       <c r="AQ53" s="42"/>
       <c r="AR53" s="43"/>
-      <c r="AS53" s="128">
-        <v>4166.67</v>
-      </c>
+      <c r="AS53" s="128"/>
       <c r="AT53" s="45"/>
       <c r="AU53" s="46"/>
       <c r="AV53" s="42"/>
       <c r="AW53" s="43"/>
-      <c r="AX53" s="128">
-        <v>4166.67</v>
-      </c>
+      <c r="AX53" s="128"/>
       <c r="AY53" s="45"/>
       <c r="AZ53" s="46"/>
       <c r="BA53" s="42"/>
       <c r="BB53" s="43"/>
-      <c r="BC53" s="128">
-        <v>4166.67</v>
-      </c>
+      <c r="BC53" s="128"/>
       <c r="BD53" s="45"/>
       <c r="BE53" s="46"/>
       <c r="BF53" s="42"/>
       <c r="BG53" s="43"/>
-      <c r="BH53" s="128">
-        <v>4166.67</v>
-      </c>
+      <c r="BH53" s="128"/>
       <c r="BI53" s="45"/>
       <c r="BJ53" s="46"/>
       <c r="BK53" s="42"/>
       <c r="BL53" s="43"/>
-      <c r="BM53" s="128">
-        <v>4166.67</v>
-      </c>
+      <c r="BM53" s="128"/>
       <c r="BN53" s="45"/>
       <c r="BO53" s="46"/>
       <c r="BP53" s="42"/>
       <c r="BQ53" s="43"/>
-      <c r="BR53" s="128">
-        <v>4166.67</v>
-      </c>
+      <c r="BR53" s="128"/>
       <c r="BS53" s="45"/>
       <c r="BT53" s="46"/>
       <c r="BU53" s="42"/>
       <c r="BV53" s="35">
-        <f t="shared" si="2"/>
-        <v>63103.369999999981</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="BW53" s="51"/>
       <c r="BX53" s="52"/>
@@ -7228,96 +7069,68 @@
         <v>102</v>
       </c>
       <c r="N54" s="93"/>
-      <c r="O54" s="45">
-        <v>88200</v>
-      </c>
-      <c r="P54" s="130">
-        <v>88200</v>
-      </c>
+      <c r="O54" s="45"/>
+      <c r="P54" s="130"/>
       <c r="Q54" s="41"/>
       <c r="R54" s="41"/>
       <c r="S54" s="44"/>
-      <c r="T54" s="45">
-        <v>88200</v>
-      </c>
-      <c r="U54" s="129">
-        <v>88200</v>
-      </c>
+      <c r="T54" s="45"/>
+      <c r="U54" s="129"/>
       <c r="V54" s="41"/>
       <c r="W54" s="42"/>
       <c r="X54" s="43"/>
-      <c r="Y54" s="45">
-        <v>88200</v>
-      </c>
+      <c r="Y54" s="45"/>
       <c r="Z54" s="39"/>
       <c r="AA54" s="46"/>
       <c r="AB54" s="42"/>
       <c r="AC54" s="43"/>
-      <c r="AD54" s="45">
-        <v>88200</v>
-      </c>
+      <c r="AD54" s="45"/>
       <c r="AE54" s="45"/>
       <c r="AF54" s="46"/>
       <c r="AG54" s="42"/>
       <c r="AH54" s="43"/>
-      <c r="AI54" s="45">
-        <v>88200</v>
-      </c>
+      <c r="AI54" s="45"/>
       <c r="AJ54" s="45"/>
       <c r="AK54" s="46"/>
       <c r="AL54" s="42"/>
       <c r="AM54" s="43"/>
-      <c r="AN54" s="45">
-        <v>88200</v>
-      </c>
+      <c r="AN54" s="45"/>
       <c r="AO54" s="45"/>
       <c r="AP54" s="46"/>
       <c r="AQ54" s="42"/>
       <c r="AR54" s="43"/>
-      <c r="AS54" s="45">
-        <v>88200</v>
-      </c>
+      <c r="AS54" s="45"/>
       <c r="AT54" s="45"/>
       <c r="AU54" s="46"/>
       <c r="AV54" s="42"/>
       <c r="AW54" s="43"/>
-      <c r="AX54" s="45">
-        <v>88200</v>
-      </c>
+      <c r="AX54" s="45"/>
       <c r="AY54" s="45"/>
       <c r="AZ54" s="46"/>
       <c r="BA54" s="42"/>
       <c r="BB54" s="43"/>
-      <c r="BC54" s="45">
-        <v>88200</v>
-      </c>
+      <c r="BC54" s="45"/>
       <c r="BD54" s="45"/>
       <c r="BE54" s="46"/>
       <c r="BF54" s="42"/>
       <c r="BG54" s="43"/>
-      <c r="BH54" s="45">
-        <v>88200</v>
-      </c>
+      <c r="BH54" s="45"/>
       <c r="BI54" s="45"/>
       <c r="BJ54" s="46"/>
       <c r="BK54" s="42"/>
       <c r="BL54" s="43"/>
-      <c r="BM54" s="45">
-        <v>88200</v>
-      </c>
+      <c r="BM54" s="45"/>
       <c r="BN54" s="45"/>
       <c r="BO54" s="46"/>
       <c r="BP54" s="42"/>
       <c r="BQ54" s="43"/>
-      <c r="BR54" s="45">
-        <v>88200</v>
-      </c>
+      <c r="BR54" s="45"/>
       <c r="BS54" s="45"/>
       <c r="BT54" s="46"/>
       <c r="BU54" s="42"/>
       <c r="BV54" s="35">
-        <f t="shared" si="2"/>
-        <v>1058400</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="BW54" s="51"/>
       <c r="BX54" s="52"/>
@@ -7363,94 +7176,68 @@
         <v>102</v>
       </c>
       <c r="N55" s="93"/>
-      <c r="O55" s="45">
-        <v>48116</v>
-      </c>
+      <c r="O55" s="45"/>
       <c r="P55" s="45"/>
       <c r="Q55" s="41"/>
       <c r="R55" s="41"/>
       <c r="S55" s="44"/>
-      <c r="T55" s="45">
-        <v>48116</v>
-      </c>
-      <c r="U55" s="129">
-        <v>84071.98</v>
-      </c>
+      <c r="T55" s="45"/>
+      <c r="U55" s="129"/>
       <c r="V55" s="41"/>
       <c r="W55" s="42"/>
       <c r="X55" s="43"/>
-      <c r="Y55" s="45">
-        <v>48116</v>
-      </c>
+      <c r="Y55" s="45"/>
       <c r="Z55" s="39"/>
       <c r="AA55" s="46"/>
       <c r="AB55" s="42"/>
       <c r="AC55" s="43"/>
-      <c r="AD55" s="45">
-        <v>48116</v>
-      </c>
+      <c r="AD55" s="45"/>
       <c r="AE55" s="45"/>
       <c r="AF55" s="46"/>
       <c r="AG55" s="42"/>
       <c r="AH55" s="43"/>
-      <c r="AI55" s="45">
-        <v>48116</v>
-      </c>
+      <c r="AI55" s="45"/>
       <c r="AJ55" s="45"/>
       <c r="AK55" s="46"/>
       <c r="AL55" s="42"/>
       <c r="AM55" s="43"/>
-      <c r="AN55" s="45">
-        <v>48116</v>
-      </c>
+      <c r="AN55" s="45"/>
       <c r="AO55" s="45"/>
       <c r="AP55" s="46"/>
       <c r="AQ55" s="42"/>
       <c r="AR55" s="43"/>
-      <c r="AS55" s="45">
-        <v>48116</v>
-      </c>
+      <c r="AS55" s="45"/>
       <c r="AT55" s="45"/>
       <c r="AU55" s="46"/>
       <c r="AV55" s="42"/>
       <c r="AW55" s="43"/>
-      <c r="AX55" s="45">
-        <v>48116</v>
-      </c>
+      <c r="AX55" s="45"/>
       <c r="AY55" s="45"/>
       <c r="AZ55" s="46"/>
       <c r="BA55" s="42"/>
       <c r="BB55" s="43"/>
-      <c r="BC55" s="45">
-        <v>48116</v>
-      </c>
+      <c r="BC55" s="45"/>
       <c r="BD55" s="45"/>
       <c r="BE55" s="46"/>
       <c r="BF55" s="42"/>
       <c r="BG55" s="43"/>
-      <c r="BH55" s="45">
-        <v>48116</v>
-      </c>
+      <c r="BH55" s="45"/>
       <c r="BI55" s="45"/>
       <c r="BJ55" s="46"/>
       <c r="BK55" s="42"/>
       <c r="BL55" s="43"/>
-      <c r="BM55" s="45">
-        <v>48116</v>
-      </c>
+      <c r="BM55" s="45"/>
       <c r="BN55" s="45"/>
       <c r="BO55" s="46"/>
       <c r="BP55" s="42"/>
       <c r="BQ55" s="43"/>
-      <c r="BR55" s="45">
-        <v>48116</v>
-      </c>
+      <c r="BR55" s="45"/>
       <c r="BS55" s="45"/>
       <c r="BT55" s="46"/>
       <c r="BU55" s="42"/>
       <c r="BV55" s="35">
-        <f t="shared" si="2"/>
-        <v>613347.98</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="BW55" s="51"/>
       <c r="BX55" s="52"/>
@@ -7496,94 +7283,68 @@
         <v>102</v>
       </c>
       <c r="N56" s="93"/>
-      <c r="O56" s="45">
-        <v>3000</v>
-      </c>
+      <c r="O56" s="45"/>
       <c r="P56" s="45"/>
       <c r="Q56" s="41"/>
       <c r="R56" s="41"/>
       <c r="S56" s="44"/>
-      <c r="T56" s="45">
-        <v>3000</v>
-      </c>
-      <c r="U56" s="129">
-        <v>5241.76</v>
-      </c>
+      <c r="T56" s="45"/>
+      <c r="U56" s="129"/>
       <c r="V56" s="41"/>
       <c r="W56" s="42"/>
       <c r="X56" s="43"/>
-      <c r="Y56" s="45">
-        <v>3000</v>
-      </c>
+      <c r="Y56" s="45"/>
       <c r="Z56" s="39"/>
       <c r="AA56" s="46"/>
       <c r="AB56" s="42"/>
       <c r="AC56" s="43"/>
-      <c r="AD56" s="45">
-        <v>3000</v>
-      </c>
+      <c r="AD56" s="45"/>
       <c r="AE56" s="45"/>
       <c r="AF56" s="46"/>
       <c r="AG56" s="42"/>
       <c r="AH56" s="43"/>
-      <c r="AI56" s="45">
-        <v>3000</v>
-      </c>
+      <c r="AI56" s="45"/>
       <c r="AJ56" s="45"/>
       <c r="AK56" s="46"/>
       <c r="AL56" s="42"/>
       <c r="AM56" s="43"/>
-      <c r="AN56" s="45">
-        <v>3000</v>
-      </c>
+      <c r="AN56" s="45"/>
       <c r="AO56" s="45"/>
       <c r="AP56" s="46"/>
       <c r="AQ56" s="42"/>
       <c r="AR56" s="43"/>
-      <c r="AS56" s="45">
-        <v>3000</v>
-      </c>
+      <c r="AS56" s="45"/>
       <c r="AT56" s="45"/>
       <c r="AU56" s="46"/>
       <c r="AV56" s="42"/>
       <c r="AW56" s="43"/>
-      <c r="AX56" s="45">
-        <v>3000</v>
-      </c>
+      <c r="AX56" s="45"/>
       <c r="AY56" s="45"/>
       <c r="AZ56" s="46"/>
       <c r="BA56" s="42"/>
       <c r="BB56" s="43"/>
-      <c r="BC56" s="45">
-        <v>3000</v>
-      </c>
+      <c r="BC56" s="45"/>
       <c r="BD56" s="45"/>
       <c r="BE56" s="46"/>
       <c r="BF56" s="42"/>
       <c r="BG56" s="43"/>
-      <c r="BH56" s="45">
-        <v>3000</v>
-      </c>
+      <c r="BH56" s="45"/>
       <c r="BI56" s="45"/>
       <c r="BJ56" s="46"/>
       <c r="BK56" s="42"/>
       <c r="BL56" s="43"/>
-      <c r="BM56" s="45">
-        <v>3000</v>
-      </c>
+      <c r="BM56" s="45"/>
       <c r="BN56" s="45"/>
       <c r="BO56" s="46"/>
       <c r="BP56" s="42"/>
       <c r="BQ56" s="43"/>
-      <c r="BR56" s="45">
-        <v>3000</v>
-      </c>
+      <c r="BR56" s="45"/>
       <c r="BS56" s="45"/>
       <c r="BT56" s="46"/>
       <c r="BU56" s="42"/>
       <c r="BV56" s="35">
-        <f t="shared" si="2"/>
-        <v>38241.760000000002</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="BW56" s="51"/>
       <c r="BX56" s="52"/>
@@ -7667,7 +7428,7 @@
       <c r="BT57" s="46"/>
       <c r="BU57" s="42"/>
       <c r="BV57" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW57" s="51"/>
@@ -7752,7 +7513,7 @@
       <c r="BT58" s="46"/>
       <c r="BU58" s="42"/>
       <c r="BV58" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW58" s="51"/>
@@ -7859,7 +7620,7 @@
       <c r="BT59" s="46"/>
       <c r="BU59" s="42"/>
       <c r="BV59" s="35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW59" s="51"/>
@@ -7906,94 +7667,68 @@
         <v>102</v>
       </c>
       <c r="N60" s="93"/>
-      <c r="O60" s="45">
-        <v>36083</v>
-      </c>
+      <c r="O60" s="45"/>
       <c r="P60" s="45"/>
       <c r="Q60" s="41"/>
       <c r="R60" s="41"/>
       <c r="S60" s="44"/>
-      <c r="T60" s="45">
-        <v>36083</v>
-      </c>
-      <c r="U60" s="129">
-        <v>63047</v>
-      </c>
+      <c r="T60" s="45"/>
+      <c r="U60" s="129"/>
       <c r="V60" s="41"/>
       <c r="W60" s="42"/>
       <c r="X60" s="43"/>
-      <c r="Y60" s="45">
-        <v>36083</v>
-      </c>
+      <c r="Y60" s="45"/>
       <c r="Z60" s="39"/>
       <c r="AA60" s="46"/>
       <c r="AB60" s="42"/>
       <c r="AC60" s="43"/>
-      <c r="AD60" s="45">
-        <v>36083</v>
-      </c>
+      <c r="AD60" s="45"/>
       <c r="AE60" s="45"/>
       <c r="AF60" s="46"/>
       <c r="AG60" s="42"/>
       <c r="AH60" s="43"/>
-      <c r="AI60" s="45">
-        <v>36083</v>
-      </c>
+      <c r="AI60" s="45"/>
       <c r="AJ60" s="45"/>
       <c r="AK60" s="46"/>
       <c r="AL60" s="42"/>
       <c r="AM60" s="43"/>
-      <c r="AN60" s="45">
-        <v>36083</v>
-      </c>
+      <c r="AN60" s="45"/>
       <c r="AO60" s="45"/>
       <c r="AP60" s="46"/>
       <c r="AQ60" s="42"/>
       <c r="AR60" s="43"/>
-      <c r="AS60" s="45">
-        <v>36083</v>
-      </c>
+      <c r="AS60" s="45"/>
       <c r="AT60" s="45"/>
       <c r="AU60" s="46"/>
       <c r="AV60" s="42"/>
       <c r="AW60" s="43"/>
-      <c r="AX60" s="45">
-        <v>36083</v>
-      </c>
+      <c r="AX60" s="45"/>
       <c r="AY60" s="45"/>
       <c r="AZ60" s="46"/>
       <c r="BA60" s="42"/>
       <c r="BB60" s="43"/>
-      <c r="BC60" s="45">
-        <v>36083</v>
-      </c>
+      <c r="BC60" s="45"/>
       <c r="BD60" s="45"/>
       <c r="BE60" s="46"/>
       <c r="BF60" s="42"/>
       <c r="BG60" s="43"/>
-      <c r="BH60" s="45">
-        <v>36083</v>
-      </c>
+      <c r="BH60" s="45"/>
       <c r="BI60" s="45"/>
       <c r="BJ60" s="46"/>
       <c r="BK60" s="42"/>
       <c r="BL60" s="43"/>
-      <c r="BM60" s="45">
-        <v>36083</v>
-      </c>
+      <c r="BM60" s="45"/>
       <c r="BN60" s="45"/>
       <c r="BO60" s="46"/>
       <c r="BP60" s="42"/>
       <c r="BQ60" s="43"/>
-      <c r="BR60" s="45">
-        <v>36083</v>
-      </c>
+      <c r="BR60" s="45"/>
       <c r="BS60" s="45"/>
       <c r="BT60" s="46"/>
       <c r="BU60" s="42"/>
       <c r="BV60" s="35">
-        <f t="shared" si="2"/>
-        <v>459960</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="BW60" s="51"/>
       <c r="BX60" s="52"/>
@@ -8039,94 +7774,68 @@
         <v>102</v>
       </c>
       <c r="N61" s="93"/>
-      <c r="O61" s="45">
-        <v>27992</v>
-      </c>
+      <c r="O61" s="45"/>
       <c r="P61" s="45"/>
       <c r="Q61" s="41"/>
       <c r="R61" s="41"/>
       <c r="S61" s="44"/>
-      <c r="T61" s="45">
-        <v>27992</v>
-      </c>
-      <c r="U61" s="129">
-        <v>48909.1</v>
-      </c>
+      <c r="T61" s="45"/>
+      <c r="U61" s="129"/>
       <c r="V61" s="41"/>
       <c r="W61" s="42"/>
       <c r="X61" s="43"/>
-      <c r="Y61" s="45">
-        <v>27992</v>
-      </c>
+      <c r="Y61" s="45"/>
       <c r="Z61" s="39"/>
       <c r="AA61" s="46"/>
       <c r="AB61" s="42"/>
       <c r="AC61" s="43"/>
-      <c r="AD61" s="45">
-        <v>27992</v>
-      </c>
+      <c r="AD61" s="45"/>
       <c r="AE61" s="45"/>
       <c r="AF61" s="46"/>
       <c r="AG61" s="42"/>
       <c r="AH61" s="43"/>
-      <c r="AI61" s="45">
-        <v>27992</v>
-      </c>
+      <c r="AI61" s="45"/>
       <c r="AJ61" s="45"/>
       <c r="AK61" s="46"/>
       <c r="AL61" s="42"/>
       <c r="AM61" s="43"/>
-      <c r="AN61" s="45">
-        <v>27992</v>
-      </c>
+      <c r="AN61" s="45"/>
       <c r="AO61" s="45"/>
       <c r="AP61" s="46"/>
       <c r="AQ61" s="42"/>
       <c r="AR61" s="43"/>
-      <c r="AS61" s="45">
-        <v>27992</v>
-      </c>
+      <c r="AS61" s="45"/>
       <c r="AT61" s="45"/>
       <c r="AU61" s="46"/>
       <c r="AV61" s="42"/>
       <c r="AW61" s="43"/>
-      <c r="AX61" s="45">
-        <v>27992</v>
-      </c>
+      <c r="AX61" s="45"/>
       <c r="AY61" s="45"/>
       <c r="AZ61" s="46"/>
       <c r="BA61" s="42"/>
       <c r="BB61" s="43"/>
-      <c r="BC61" s="45">
-        <v>27992</v>
-      </c>
+      <c r="BC61" s="45"/>
       <c r="BD61" s="45"/>
       <c r="BE61" s="46"/>
       <c r="BF61" s="42"/>
       <c r="BG61" s="43"/>
-      <c r="BH61" s="45">
-        <v>27992</v>
-      </c>
+      <c r="BH61" s="45"/>
       <c r="BI61" s="45"/>
       <c r="BJ61" s="46"/>
       <c r="BK61" s="42"/>
       <c r="BL61" s="43"/>
-      <c r="BM61" s="45">
-        <v>27992</v>
-      </c>
+      <c r="BM61" s="45"/>
       <c r="BN61" s="45"/>
       <c r="BO61" s="46"/>
       <c r="BP61" s="42"/>
       <c r="BQ61" s="43"/>
-      <c r="BR61" s="45">
-        <v>27992</v>
-      </c>
+      <c r="BR61" s="45"/>
       <c r="BS61" s="45"/>
       <c r="BT61" s="46"/>
       <c r="BU61" s="42"/>
       <c r="BV61" s="35">
-        <f t="shared" si="2"/>
-        <v>356821.1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="BW61" s="51"/>
       <c r="BX61" s="52"/>
@@ -8171,133 +7880,77 @@
       <c r="M62" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="N62" s="92"/>
+      <c r="N62" s="92">
+        <v>0</v>
+      </c>
       <c r="O62" s="39">
-        <v>31350</v>
-      </c>
-      <c r="P62" s="39"/>
+        <v>0</v>
+      </c>
+      <c r="P62" s="39">
+        <v>25838</v>
+      </c>
       <c r="Q62" s="81">
         <v>31350</v>
       </c>
-      <c r="R62" s="41">
-        <f t="shared" si="3"/>
-        <v>-31350</v>
-      </c>
+      <c r="R62" s="41"/>
       <c r="S62" s="40"/>
-      <c r="T62" s="39">
-        <v>31350</v>
-      </c>
-      <c r="U62" s="39">
-        <v>23416.38</v>
-      </c>
+      <c r="T62" s="39"/>
+      <c r="U62" s="39"/>
       <c r="V62" s="41"/>
-      <c r="W62" s="42">
-        <f t="shared" si="0"/>
-        <v>23416.38</v>
-      </c>
+      <c r="W62" s="42"/>
       <c r="X62" s="43"/>
-      <c r="Y62" s="39">
-        <v>31350</v>
-      </c>
+      <c r="Y62" s="39"/>
       <c r="Z62" s="39"/>
       <c r="AA62" s="41"/>
-      <c r="AB62" s="42">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+      <c r="AB62" s="42"/>
       <c r="AC62" s="43"/>
-      <c r="AD62" s="39">
-        <v>31350</v>
-      </c>
+      <c r="AD62" s="39"/>
       <c r="AE62" s="39"/>
       <c r="AF62" s="41"/>
-      <c r="AG62" s="42">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="AG62" s="42"/>
       <c r="AH62" s="43"/>
-      <c r="AI62" s="39">
-        <v>31350</v>
-      </c>
+      <c r="AI62" s="39"/>
       <c r="AJ62" s="39"/>
       <c r="AK62" s="41"/>
-      <c r="AL62" s="42">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
+      <c r="AL62" s="42"/>
       <c r="AM62" s="43"/>
-      <c r="AN62" s="39">
-        <v>31350</v>
-      </c>
+      <c r="AN62" s="39"/>
       <c r="AO62" s="39"/>
       <c r="AP62" s="41"/>
-      <c r="AQ62" s="42">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
+      <c r="AQ62" s="42"/>
       <c r="AR62" s="43"/>
-      <c r="AS62" s="39">
-        <v>31350</v>
-      </c>
+      <c r="AS62" s="39"/>
       <c r="AT62" s="39"/>
       <c r="AU62" s="41"/>
-      <c r="AV62" s="42">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="AV62" s="42"/>
       <c r="AW62" s="43"/>
-      <c r="AX62" s="39">
-        <v>31350</v>
-      </c>
+      <c r="AX62" s="39"/>
       <c r="AY62" s="39"/>
       <c r="AZ62" s="41"/>
-      <c r="BA62" s="42">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="BA62" s="42"/>
       <c r="BB62" s="43"/>
-      <c r="BC62" s="39">
-        <v>31350</v>
-      </c>
+      <c r="BC62" s="39"/>
       <c r="BD62" s="39"/>
       <c r="BE62" s="41"/>
-      <c r="BF62" s="42">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
+      <c r="BF62" s="42"/>
       <c r="BG62" s="43"/>
-      <c r="BH62" s="39">
-        <v>31350</v>
-      </c>
+      <c r="BH62" s="39"/>
       <c r="BI62" s="39"/>
       <c r="BJ62" s="41"/>
-      <c r="BK62" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
+      <c r="BK62" s="42"/>
       <c r="BL62" s="43"/>
-      <c r="BM62" s="39">
-        <v>31350</v>
-      </c>
+      <c r="BM62" s="39"/>
       <c r="BN62" s="39"/>
       <c r="BO62" s="41"/>
-      <c r="BP62" s="42">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
+      <c r="BP62" s="42"/>
       <c r="BQ62" s="43"/>
-      <c r="BR62" s="39">
-        <v>31350</v>
-      </c>
+      <c r="BR62" s="39"/>
       <c r="BS62" s="39"/>
       <c r="BT62" s="41"/>
-      <c r="BU62" s="42">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="BU62" s="42"/>
       <c r="BV62" s="35">
-        <f t="shared" si="2"/>
-        <v>368266.38</v>
+        <f t="shared" si="0"/>
+        <v>31350</v>
       </c>
       <c r="BW62" s="51"/>
       <c r="BX62" s="52"/>
@@ -8342,109 +7995,77 @@
       <c r="M63" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="N63" s="92"/>
-      <c r="O63" s="39"/>
-      <c r="P63" s="39"/>
+      <c r="N63" s="92">
+        <v>-146492.82999999999</v>
+      </c>
+      <c r="O63" s="39">
+        <v>23578</v>
+      </c>
+      <c r="P63" s="39">
+        <v>0</v>
+      </c>
       <c r="Q63" s="81">
-        <v>23578</v>
-      </c>
-      <c r="R63" s="41">
-        <f t="shared" si="3"/>
-        <v>-23578</v>
-      </c>
+        <v>115764.16</v>
+      </c>
+      <c r="R63" s="41"/>
       <c r="S63" s="40"/>
       <c r="T63" s="39"/>
       <c r="U63" s="39"/>
-      <c r="V63" s="81">
-        <v>122914.66</v>
-      </c>
-      <c r="W63" s="42">
-        <f t="shared" si="0"/>
-        <v>-122914.66</v>
-      </c>
+      <c r="V63" s="81"/>
+      <c r="W63" s="42"/>
       <c r="X63" s="43"/>
       <c r="Y63" s="39"/>
       <c r="Z63" s="39"/>
       <c r="AA63" s="41"/>
-      <c r="AB63" s="42">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+      <c r="AB63" s="42"/>
       <c r="AC63" s="43"/>
       <c r="AD63" s="39"/>
       <c r="AE63" s="39"/>
       <c r="AF63" s="39"/>
-      <c r="AG63" s="42">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="AG63" s="42"/>
       <c r="AH63" s="43"/>
       <c r="AI63" s="39"/>
       <c r="AJ63" s="39"/>
       <c r="AK63" s="39"/>
-      <c r="AL63" s="42">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
+      <c r="AL63" s="42"/>
       <c r="AM63" s="43"/>
       <c r="AN63" s="39"/>
       <c r="AO63" s="39"/>
       <c r="AP63" s="39"/>
-      <c r="AQ63" s="42">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
+      <c r="AQ63" s="42"/>
       <c r="AR63" s="43"/>
       <c r="AS63" s="39"/>
       <c r="AT63" s="39"/>
       <c r="AU63" s="39"/>
-      <c r="AV63" s="42">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="AV63" s="42"/>
       <c r="AW63" s="43"/>
       <c r="AX63" s="39"/>
       <c r="AY63" s="39"/>
       <c r="AZ63" s="39"/>
-      <c r="BA63" s="42">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="BA63" s="42"/>
       <c r="BB63" s="43"/>
       <c r="BC63" s="39"/>
       <c r="BD63" s="39"/>
       <c r="BE63" s="39"/>
-      <c r="BF63" s="42">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
+      <c r="BF63" s="42"/>
       <c r="BG63" s="43"/>
       <c r="BH63" s="39"/>
       <c r="BI63" s="39"/>
       <c r="BJ63" s="39"/>
-      <c r="BK63" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
+      <c r="BK63" s="42"/>
       <c r="BL63" s="43"/>
       <c r="BM63" s="39"/>
       <c r="BN63" s="39"/>
       <c r="BO63" s="39"/>
-      <c r="BP63" s="42">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
+      <c r="BP63" s="42"/>
       <c r="BQ63" s="43"/>
       <c r="BR63" s="39"/>
       <c r="BS63" s="39"/>
       <c r="BT63" s="39"/>
-      <c r="BU63" s="42">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="BU63" s="42"/>
       <c r="BV63" s="35">
-        <f t="shared" si="2"/>
-        <v>146492.66</v>
+        <f t="shared" si="0"/>
+        <v>115764.16</v>
       </c>
       <c r="BW63" s="92"/>
       <c r="BX63" s="52"/>
@@ -8489,127 +8110,77 @@
       <c r="M64" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="N64" s="92"/>
-      <c r="O64" s="39"/>
-      <c r="P64" s="39"/>
-      <c r="Q64" s="41"/>
-      <c r="R64" s="41">
-        <f t="shared" si="3"/>
+      <c r="N64" s="92">
         <v>0</v>
       </c>
+      <c r="O64" s="39">
+        <v>0</v>
+      </c>
+      <c r="P64" s="39">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="41">
+        <v>0</v>
+      </c>
+      <c r="R64" s="41"/>
       <c r="S64" s="40"/>
-      <c r="T64" s="39">
-        <v>5786</v>
-      </c>
+      <c r="T64" s="39"/>
       <c r="U64" s="39"/>
       <c r="V64" s="41"/>
-      <c r="W64" s="42">
+      <c r="W64" s="42"/>
+      <c r="X64" s="43"/>
+      <c r="Y64" s="39"/>
+      <c r="Z64" s="39"/>
+      <c r="AA64" s="41"/>
+      <c r="AB64" s="42"/>
+      <c r="AC64" s="43"/>
+      <c r="AD64" s="39"/>
+      <c r="AE64" s="39"/>
+      <c r="AF64" s="41"/>
+      <c r="AG64" s="42"/>
+      <c r="AH64" s="43"/>
+      <c r="AI64" s="39"/>
+      <c r="AJ64" s="39"/>
+      <c r="AK64" s="41"/>
+      <c r="AL64" s="42"/>
+      <c r="AM64" s="43"/>
+      <c r="AN64" s="39"/>
+      <c r="AO64" s="39"/>
+      <c r="AP64" s="41"/>
+      <c r="AQ64" s="42"/>
+      <c r="AR64" s="43"/>
+      <c r="AS64" s="39"/>
+      <c r="AT64" s="39"/>
+      <c r="AU64" s="41"/>
+      <c r="AV64" s="42"/>
+      <c r="AW64" s="43"/>
+      <c r="AX64" s="39"/>
+      <c r="AY64" s="39"/>
+      <c r="AZ64" s="41"/>
+      <c r="BA64" s="42"/>
+      <c r="BB64" s="43"/>
+      <c r="BC64" s="39"/>
+      <c r="BD64" s="39"/>
+      <c r="BE64" s="41"/>
+      <c r="BF64" s="42"/>
+      <c r="BG64" s="43"/>
+      <c r="BH64" s="39"/>
+      <c r="BI64" s="39"/>
+      <c r="BJ64" s="41"/>
+      <c r="BK64" s="42"/>
+      <c r="BL64" s="43"/>
+      <c r="BM64" s="39"/>
+      <c r="BN64" s="39"/>
+      <c r="BO64" s="41"/>
+      <c r="BP64" s="42"/>
+      <c r="BQ64" s="43"/>
+      <c r="BR64" s="39"/>
+      <c r="BS64" s="39"/>
+      <c r="BT64" s="41"/>
+      <c r="BU64" s="42"/>
+      <c r="BV64" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
-      </c>
-      <c r="X64" s="43"/>
-      <c r="Y64" s="39">
-        <v>5786</v>
-      </c>
-      <c r="Z64" s="39"/>
-      <c r="AA64" s="41"/>
-      <c r="AB64" s="42">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AC64" s="43"/>
-      <c r="AD64" s="39">
-        <v>5786</v>
-      </c>
-      <c r="AE64" s="39"/>
-      <c r="AF64" s="41"/>
-      <c r="AG64" s="42">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AH64" s="43"/>
-      <c r="AI64" s="39">
-        <v>5786</v>
-      </c>
-      <c r="AJ64" s="39"/>
-      <c r="AK64" s="41"/>
-      <c r="AL64" s="42">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AM64" s="43"/>
-      <c r="AN64" s="39">
-        <v>5786</v>
-      </c>
-      <c r="AO64" s="39"/>
-      <c r="AP64" s="41"/>
-      <c r="AQ64" s="42">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AR64" s="43"/>
-      <c r="AS64" s="39">
-        <v>5786</v>
-      </c>
-      <c r="AT64" s="39"/>
-      <c r="AU64" s="41"/>
-      <c r="AV64" s="42">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AW64" s="43"/>
-      <c r="AX64" s="39">
-        <v>5786</v>
-      </c>
-      <c r="AY64" s="39"/>
-      <c r="AZ64" s="41"/>
-      <c r="BA64" s="42">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="BB64" s="43"/>
-      <c r="BC64" s="39">
-        <v>5786</v>
-      </c>
-      <c r="BD64" s="39"/>
-      <c r="BE64" s="41"/>
-      <c r="BF64" s="42">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="BG64" s="43"/>
-      <c r="BH64" s="39">
-        <v>5786</v>
-      </c>
-      <c r="BI64" s="39"/>
-      <c r="BJ64" s="41"/>
-      <c r="BK64" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BL64" s="43"/>
-      <c r="BM64" s="39">
-        <v>5786</v>
-      </c>
-      <c r="BN64" s="39"/>
-      <c r="BO64" s="41"/>
-      <c r="BP64" s="42">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BQ64" s="43"/>
-      <c r="BR64" s="39">
-        <v>5786</v>
-      </c>
-      <c r="BS64" s="39"/>
-      <c r="BT64" s="41"/>
-      <c r="BU64" s="42">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BV64" s="35">
-        <f t="shared" si="2"/>
-        <v>63646</v>
       </c>
       <c r="BW64" s="51"/>
       <c r="BX64" s="52"/>
@@ -8630,20 +8201,12 @@
       <c r="K65" s="105"/>
       <c r="L65" s="103"/>
       <c r="M65" s="106"/>
-      <c r="N65" s="58">
-        <v>10975</v>
-      </c>
+      <c r="N65" s="58"/>
       <c r="O65" s="53"/>
       <c r="P65" s="53"/>
       <c r="Q65" s="55"/>
-      <c r="R65" s="55" t="str">
-        <f>IF(OR(P65="",Q65=""),"",P65-Q65)</f>
-        <v/>
-      </c>
-      <c r="S65" s="54">
-        <f>10126+10107</f>
-        <v>20233</v>
-      </c>
+      <c r="R65" s="55"/>
+      <c r="S65" s="54"/>
       <c r="T65" s="53"/>
       <c r="U65" s="53"/>
       <c r="V65" s="55"/>
@@ -8657,76 +8220,49 @@
       <c r="AD65" s="53"/>
       <c r="AE65" s="53"/>
       <c r="AF65" s="55"/>
-      <c r="AG65" s="56" t="str">
-        <f t="shared" ref="AG65" si="13">IF(OR(AE65="",AF65=""),"",AE65-AF65)</f>
-        <v/>
-      </c>
+      <c r="AG65" s="56"/>
       <c r="AH65" s="57"/>
       <c r="AI65" s="53"/>
       <c r="AJ65" s="53"/>
       <c r="AK65" s="55"/>
-      <c r="AL65" s="56" t="str">
-        <f t="shared" ref="AL65" si="14">IF(OR(AJ65="",AK65=""),"",AJ65-AK65)</f>
-        <v/>
-      </c>
+      <c r="AL65" s="56"/>
       <c r="AM65" s="57"/>
       <c r="AN65" s="53"/>
       <c r="AO65" s="53"/>
       <c r="AP65" s="55"/>
-      <c r="AQ65" s="56" t="str">
-        <f t="shared" ref="AQ65" si="15">IF(OR(AO65="",AP65=""),"",AO65-AP65)</f>
-        <v/>
-      </c>
+      <c r="AQ65" s="56"/>
       <c r="AR65" s="57"/>
       <c r="AS65" s="53"/>
       <c r="AT65" s="53"/>
       <c r="AU65" s="55"/>
-      <c r="AV65" s="56" t="str">
-        <f t="shared" ref="AV65" si="16">IF(OR(AT65="",AU65=""),"",AT65-AU65)</f>
-        <v/>
-      </c>
+      <c r="AV65" s="56"/>
       <c r="AW65" s="57"/>
       <c r="AX65" s="53"/>
       <c r="AY65" s="53"/>
       <c r="AZ65" s="55"/>
-      <c r="BA65" s="56" t="str">
-        <f t="shared" ref="BA65" si="17">IF(OR(AY65="",AZ65=""),"",AY65-AZ65)</f>
-        <v/>
-      </c>
+      <c r="BA65" s="56"/>
       <c r="BB65" s="57"/>
       <c r="BC65" s="53"/>
       <c r="BD65" s="53"/>
       <c r="BE65" s="55"/>
-      <c r="BF65" s="56" t="str">
-        <f t="shared" ref="BF65" si="18">IF(OR(BD65="",BE65=""),"",BD65-BE65)</f>
-        <v/>
-      </c>
+      <c r="BF65" s="56"/>
       <c r="BG65" s="57"/>
       <c r="BH65" s="53"/>
       <c r="BI65" s="53"/>
       <c r="BJ65" s="55"/>
-      <c r="BK65" s="56" t="str">
-        <f t="shared" ref="BK65" si="19">IF(OR(BI65="",BJ65=""),"",BI65-BJ65)</f>
-        <v/>
-      </c>
+      <c r="BK65" s="56"/>
       <c r="BL65" s="57"/>
       <c r="BM65" s="53"/>
       <c r="BN65" s="53"/>
       <c r="BO65" s="55"/>
-      <c r="BP65" s="56" t="str">
-        <f t="shared" ref="BP65" si="20">IF(OR(BN65="",BO65=""),"",BN65-BO65)</f>
-        <v/>
-      </c>
+      <c r="BP65" s="56"/>
       <c r="BQ65" s="57"/>
       <c r="BR65" s="53"/>
       <c r="BS65" s="53"/>
       <c r="BT65" s="55"/>
-      <c r="BU65" s="56" t="str">
-        <f t="shared" ref="BU65" si="21">IF(OR(BS65="",BT65=""),"",BS65-BT65)</f>
-        <v/>
-      </c>
+      <c r="BU65" s="56"/>
       <c r="BV65" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BW65" s="58"/>
@@ -8839,24 +8375,29 @@
     <mergeCell ref="AR14:AV14"/>
     <mergeCell ref="AW14:BA14"/>
   </mergeCells>
-  <conditionalFormatting sqref="Q17:Q65 V17:V65 AA17:AA65 AF17:AF65 AK17:AK65 AP17:AP65 AU17:AU65 AZ17:AZ65 BE17:BE65 BJ17:BJ65 BO17:BO65 BT17:BT65">
-    <cfRule type="expression" dxfId="3" priority="8">
+  <conditionalFormatting sqref="Q65 V17:V65 AA17:AA65 AF17:AF65 AK17:AK65 AP17:AP65 AU17:AU65 AZ17:AZ65 BE17:BE65 BJ17:BJ65 BO17:BO65 BT17:BT65">
+    <cfRule type="expression" dxfId="4" priority="9">
       <formula>IF(AND(P17&gt;0,Q17=0),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BT12 V17:X65 AB17:AC65 AG17:AH65 AL17:AM65 AQ17:AR65 AV17:AW65 BA17:BB65 BF17:BG65 BK17:BL65 BP17:BQ65 BU17:BU65">
-    <cfRule type="expression" dxfId="2" priority="9">
+    <cfRule type="expression" dxfId="3" priority="10">
       <formula>IF(AND(U12&lt;&gt;"",V12="",TODAY()&gt;DATE(YEAR(TODAY()),MONTH(DATEVALUE("1-"&amp;LEFT(#REF!,3)&amp;"-1900")),20)),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BV17:BV64">
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>90%*$K$17</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BW13:BW14">
-    <cfRule type="expression" dxfId="0" priority="7">
+    <cfRule type="expression" dxfId="1" priority="8">
       <formula>IF(BW13&lt;0,TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q17:Q64">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>IF(AND(P17&gt;0,Q17=0),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/templates/Ram 2026_Owen Testing.xlsx
+++ b/data/templates/Ram 2026_Owen Testing.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pfizer-my.sharepoint.com/personal/hoveyo_pfizer_com/Documents/financial-automation-project/data/templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pfizer-my.sharepoint.com/personal/oelkem01_pfizer_com/Documents/SVO/financial-automation-project/data/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{7A1710ED-9570-4990-9C3D-DDE87217A9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89BC7557-4DC5-4339-B664-F1819F265931}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{7A1710ED-9570-4990-9C3D-DDE87217A9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFC4670C-9C6F-4343-9F6E-82C4BEE20647}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12480" tabRatio="590" xr2:uid="{0996C49B-04E6-42AE-AA83-2F64BE89A626}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="22920" windowHeight="14250" tabRatio="590" xr2:uid="{0996C49B-04E6-42AE-AA83-2F64BE89A626}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="5" r:id="rId1"/>
@@ -2292,12 +2292,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2306,6 +2300,21 @@
     </xf>
     <xf numFmtId="3" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -2325,15 +2334,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Currency 2" xfId="2" xr:uid="{C819F491-96B6-415F-B3EE-ED5A59A1E95E}"/>
@@ -2345,7 +2345,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF7C80"/>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2359,7 +2359,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFF7C80"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2969,10 +2969,10 @@
       <c r="U7" s="14"/>
     </row>
     <row r="8" spans="1:77" x14ac:dyDescent="0.25">
-      <c r="A8" s="138" t="s">
+      <c r="A8" s="144" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="139"/>
+      <c r="B8" s="145"/>
       <c r="C8" s="78"/>
       <c r="D8" s="83" t="s">
         <v>8</v>
@@ -3059,112 +3059,112 @@
       <c r="I13" s="68"/>
       <c r="J13" s="68"/>
       <c r="K13" s="72"/>
-      <c r="L13" s="143" t="s">
+      <c r="L13" s="146" t="s">
         <v>14</v>
       </c>
-      <c r="M13" s="144"/>
-      <c r="N13" s="140" cm="1">
+      <c r="M13" s="147"/>
+      <c r="N13" s="138" cm="1">
         <f t="array" ref="N13">SUM(Q17:Q65)+SUM(_xlfn._xlws.FILTER(P17:P65,Q17:Q65=""))+SUM(_xlfn._xlws.FILTER(O17:O65,(P17:P65="")*(Q17:Q65="")))+SUMIFS(R17:R65,Q17:Q65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(N17:N65)</f>
-        <v>410369.37000000011</v>
-      </c>
-      <c r="O13" s="141"/>
-      <c r="P13" s="141"/>
-      <c r="Q13" s="141"/>
-      <c r="R13" s="142"/>
-      <c r="S13" s="140" cm="1">
+        <v>389076.24000000011</v>
+      </c>
+      <c r="O13" s="139"/>
+      <c r="P13" s="139"/>
+      <c r="Q13" s="139"/>
+      <c r="R13" s="140"/>
+      <c r="S13" s="138" cm="1">
         <f t="array" ref="S13">SUM(V17:V65)+SUM(_xlfn._xlws.FILTER(U17:U65,V17:V65=""))+SUM(_xlfn._xlws.FILTER(T17:T65,(U17:U65="")*(V17:V65="")))+SUMIFS(W17:W65,V17:V65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(S17:S65)</f>
         <v>0</v>
       </c>
-      <c r="T13" s="141"/>
-      <c r="U13" s="141"/>
-      <c r="V13" s="141"/>
-      <c r="W13" s="142"/>
-      <c r="X13" s="140" cm="1">
+      <c r="T13" s="139"/>
+      <c r="U13" s="139"/>
+      <c r="V13" s="139"/>
+      <c r="W13" s="140"/>
+      <c r="X13" s="138" cm="1">
         <f t="array" ref="X13">SUM(AA17:AA65)+SUM(_xlfn._xlws.FILTER(Z17:Z65,AA17:AA65=""))+SUM(_xlfn._xlws.FILTER(Y17:Y65,(Z17:Z65="")*(AA17:AA65="")))+SUMIFS(AB17:AB65,AA17:AA65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(X17:X65)</f>
         <v>0</v>
       </c>
-      <c r="Y13" s="141"/>
-      <c r="Z13" s="141"/>
-      <c r="AA13" s="141"/>
-      <c r="AB13" s="142"/>
-      <c r="AC13" s="140" cm="1">
+      <c r="Y13" s="139"/>
+      <c r="Z13" s="139"/>
+      <c r="AA13" s="139"/>
+      <c r="AB13" s="140"/>
+      <c r="AC13" s="138" cm="1">
         <f t="array" ref="AC13">SUM(AF17:AF65)+SUM(_xlfn._xlws.FILTER(AE17:AE65,AF17:AF65=""))+SUM(_xlfn._xlws.FILTER(AD17:AD65,(AE17:AE65="")*(AF17:AF65="")))+SUMIFS(AG17:AG65,AF17:AF65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(AC17:AC65)</f>
         <v>0</v>
       </c>
-      <c r="AD13" s="141"/>
-      <c r="AE13" s="141"/>
-      <c r="AF13" s="141"/>
-      <c r="AG13" s="142"/>
-      <c r="AH13" s="140" cm="1">
+      <c r="AD13" s="139"/>
+      <c r="AE13" s="139"/>
+      <c r="AF13" s="139"/>
+      <c r="AG13" s="140"/>
+      <c r="AH13" s="138" cm="1">
         <f t="array" ref="AH13">SUM(AK17:AK65)+SUM(_xlfn._xlws.FILTER(AJ17:AJ65,AK17:AK65=""))+SUM(_xlfn._xlws.FILTER(AI17:AI65,(AJ17:AJ65="")*(AK17:AK65="")))+SUMIFS(AL17:AL65,AK17:AK65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(AH17:AH65)</f>
         <v>0</v>
       </c>
-      <c r="AI13" s="141"/>
-      <c r="AJ13" s="141"/>
-      <c r="AK13" s="141"/>
-      <c r="AL13" s="142"/>
-      <c r="AM13" s="140" cm="1">
+      <c r="AI13" s="139"/>
+      <c r="AJ13" s="139"/>
+      <c r="AK13" s="139"/>
+      <c r="AL13" s="140"/>
+      <c r="AM13" s="138" cm="1">
         <f t="array" ref="AM13">SUM(AP17:AP65)+SUM(_xlfn._xlws.FILTER(AO17:AO65,AP17:AP65=""))+SUM(_xlfn._xlws.FILTER(AN17:AN65,(AO17:AO65="")*(AP17:AP65="")))+SUMIFS(AQ17:AQ65,AP17:AP65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(AM17:AM65)</f>
         <v>0</v>
       </c>
-      <c r="AN13" s="141"/>
-      <c r="AO13" s="141"/>
-      <c r="AP13" s="141"/>
-      <c r="AQ13" s="142"/>
-      <c r="AR13" s="140" cm="1">
+      <c r="AN13" s="139"/>
+      <c r="AO13" s="139"/>
+      <c r="AP13" s="139"/>
+      <c r="AQ13" s="140"/>
+      <c r="AR13" s="138" cm="1">
         <f t="array" ref="AR13">SUM(AU17:AU65)+SUM(_xlfn._xlws.FILTER(AT17:AT65,AU17:AU65=""))+SUM(_xlfn._xlws.FILTER(AS17:AS65,(AT17:AT65="")*(AU17:AU65="")))+SUMIFS(AV17:AV65,AU17:AU65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(AR17:AR65)</f>
         <v>0</v>
       </c>
-      <c r="AS13" s="141"/>
-      <c r="AT13" s="141"/>
-      <c r="AU13" s="141"/>
-      <c r="AV13" s="142"/>
-      <c r="AW13" s="140" cm="1">
+      <c r="AS13" s="139"/>
+      <c r="AT13" s="139"/>
+      <c r="AU13" s="139"/>
+      <c r="AV13" s="140"/>
+      <c r="AW13" s="138" cm="1">
         <f t="array" ref="AW13">SUM(AZ17:AZ65)+SUM(_xlfn._xlws.FILTER(AY17:AY65,AZ17:AZ65=""))+SUM(_xlfn._xlws.FILTER(AX17:AX65,(AY17:AY65="")*(AZ17:AZ65="")))+SUMIFS(BA17:BA65,AZ17:AZ65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(AW17:AW65)</f>
         <v>0</v>
       </c>
-      <c r="AX13" s="141"/>
-      <c r="AY13" s="141"/>
-      <c r="AZ13" s="141"/>
-      <c r="BA13" s="142"/>
-      <c r="BB13" s="140" cm="1">
+      <c r="AX13" s="139"/>
+      <c r="AY13" s="139"/>
+      <c r="AZ13" s="139"/>
+      <c r="BA13" s="140"/>
+      <c r="BB13" s="138" cm="1">
         <f t="array" ref="BB13">SUM(BE17:BE65)+SUM(_xlfn._xlws.FILTER(BD17:BD65,BE17:BE65=""))+SUM(_xlfn._xlws.FILTER(BC17:BC65,(BD17:BD65="")*(BE17:BE65="")))+SUMIFS(BF17:BF65,BE17:BE65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(BB17:BB65)</f>
         <v>0</v>
       </c>
-      <c r="BC13" s="141"/>
-      <c r="BD13" s="141"/>
-      <c r="BE13" s="141"/>
-      <c r="BF13" s="142"/>
-      <c r="BG13" s="140" cm="1">
+      <c r="BC13" s="139"/>
+      <c r="BD13" s="139"/>
+      <c r="BE13" s="139"/>
+      <c r="BF13" s="140"/>
+      <c r="BG13" s="138" cm="1">
         <f t="array" ref="BG13">SUM(BJ17:BJ65)+SUM(_xlfn._xlws.FILTER(BI17:BI65,BJ17:BJ65=""))+SUM(_xlfn._xlws.FILTER(BH17:BH65,(BI17:BI65="")*(BJ17:BJ65="")))+SUMIFS(BK17:BK65,BJ17:BJ65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(BG17:BG65)</f>
         <v>0</v>
       </c>
-      <c r="BH13" s="141"/>
-      <c r="BI13" s="141"/>
-      <c r="BJ13" s="141"/>
-      <c r="BK13" s="142"/>
-      <c r="BL13" s="140" cm="1">
+      <c r="BH13" s="139"/>
+      <c r="BI13" s="139"/>
+      <c r="BJ13" s="139"/>
+      <c r="BK13" s="140"/>
+      <c r="BL13" s="138" cm="1">
         <f t="array" ref="BL13">SUM(BO17:BO65)+SUM(_xlfn._xlws.FILTER(BN17:BN65,BO17:BO65=""))+SUM(_xlfn._xlws.FILTER(BM17:BM65,(BN17:BN65="")*(BO17:BO65="")))+SUMIFS(BP17:BP65,BO17:BO65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(BL17:BL65)</f>
         <v>0</v>
       </c>
-      <c r="BM13" s="141"/>
-      <c r="BN13" s="141"/>
-      <c r="BO13" s="141"/>
-      <c r="BP13" s="142"/>
-      <c r="BQ13" s="140" cm="1">
+      <c r="BM13" s="139"/>
+      <c r="BN13" s="139"/>
+      <c r="BO13" s="139"/>
+      <c r="BP13" s="140"/>
+      <c r="BQ13" s="138" cm="1">
         <f t="array" ref="BQ13">SUM(BT17:BT65)+SUM(_xlfn._xlws.FILTER(BS17:BS65,BT17:BT65=""))+SUM(_xlfn._xlws.FILTER(BR17:BR65,(BS17:BS65="")*(BT17:BT65="")))+SUMIFS(BU17:BU65,BT17:BT65,"&lt;&gt;"&amp;"",$P$17:$P$65,"&lt;&gt;"&amp;"")+SUM(BQ17:BQ65)</f>
         <v>0</v>
       </c>
-      <c r="BR13" s="141"/>
-      <c r="BS13" s="141"/>
-      <c r="BT13" s="141"/>
-      <c r="BU13" s="142"/>
+      <c r="BR13" s="139"/>
+      <c r="BS13" s="139"/>
+      <c r="BT13" s="139"/>
+      <c r="BU13" s="140"/>
       <c r="BV13" s="16" t="s">
         <v>15</v>
       </c>
       <c r="BW13" s="17">
         <f>BW15-BV15</f>
-        <v>-556862.20000000007</v>
+        <v>-535569.07000000007</v>
       </c>
     </row>
     <row r="14" spans="1:77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3180,106 +3180,106 @@
       <c r="K14" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="L14" s="145" t="s">
+      <c r="L14" s="148" t="s">
         <v>17</v>
       </c>
-      <c r="M14" s="146"/>
-      <c r="N14" s="140" cm="1">
+      <c r="M14" s="149"/>
+      <c r="N14" s="138" cm="1">
         <f t="array" ref="N14">SUM(Q17:Q65)+SUM(_xlfn._xlws.FILTER(P17:P65,Q17:Q65=""))+SUM(_xlfn._xlws.FILTER(O17:O65,(P17:P65="")*(Q17:Q65="")))</f>
-        <v>556862.20000000007</v>
-      </c>
-      <c r="O14" s="141"/>
-      <c r="P14" s="141"/>
-      <c r="Q14" s="141"/>
-      <c r="R14" s="142"/>
-      <c r="S14" s="140" cm="1">
+        <v>535569.07000000007</v>
+      </c>
+      <c r="O14" s="139"/>
+      <c r="P14" s="139"/>
+      <c r="Q14" s="139"/>
+      <c r="R14" s="140"/>
+      <c r="S14" s="138" cm="1">
         <f t="array" ref="S14">SUM(V17:V65)+SUM(_xlfn._xlws.FILTER(U17:U65,V17:V65=""))+SUM(_xlfn._xlws.FILTER(T17:T65,(U17:U65="")*(V17:V65="")))</f>
         <v>0</v>
       </c>
-      <c r="T14" s="141"/>
-      <c r="U14" s="141"/>
-      <c r="V14" s="141"/>
-      <c r="W14" s="142"/>
-      <c r="X14" s="140" cm="1">
+      <c r="T14" s="139"/>
+      <c r="U14" s="139"/>
+      <c r="V14" s="139"/>
+      <c r="W14" s="140"/>
+      <c r="X14" s="138" cm="1">
         <f t="array" ref="X14">SUM(AA17:AA65)+SUM(_xlfn._xlws.FILTER(Z17:Z65,AA17:AA65=""))+SUM(_xlfn._xlws.FILTER(Y17:Y65,(Z17:Z65="")*(AA17:AA65="")))</f>
         <v>0</v>
       </c>
-      <c r="Y14" s="141"/>
-      <c r="Z14" s="141"/>
-      <c r="AA14" s="141"/>
-      <c r="AB14" s="142"/>
-      <c r="AC14" s="140" cm="1">
+      <c r="Y14" s="139"/>
+      <c r="Z14" s="139"/>
+      <c r="AA14" s="139"/>
+      <c r="AB14" s="140"/>
+      <c r="AC14" s="138" cm="1">
         <f t="array" ref="AC14">SUM(AF17:AF65)+SUM(_xlfn._xlws.FILTER(AE17:AE65,AF17:AF65=""))+SUM(_xlfn._xlws.FILTER(AD17:AD65,(AE17:AE65="")*(AF17:AF65="")))</f>
         <v>0</v>
       </c>
-      <c r="AD14" s="141"/>
-      <c r="AE14" s="141"/>
-      <c r="AF14" s="141"/>
-      <c r="AG14" s="142"/>
-      <c r="AH14" s="140" cm="1">
+      <c r="AD14" s="139"/>
+      <c r="AE14" s="139"/>
+      <c r="AF14" s="139"/>
+      <c r="AG14" s="140"/>
+      <c r="AH14" s="138" cm="1">
         <f t="array" ref="AH14">SUM(AK17:AK65)+SUM(_xlfn._xlws.FILTER(AJ17:AJ65,AK17:AK65=""))+SUM(_xlfn._xlws.FILTER(AI17:AI65,(AJ17:AJ65="")*(AK17:AK65="")))</f>
         <v>0</v>
       </c>
-      <c r="AI14" s="141"/>
-      <c r="AJ14" s="141"/>
-      <c r="AK14" s="141"/>
-      <c r="AL14" s="142"/>
-      <c r="AM14" s="140" cm="1">
+      <c r="AI14" s="139"/>
+      <c r="AJ14" s="139"/>
+      <c r="AK14" s="139"/>
+      <c r="AL14" s="140"/>
+      <c r="AM14" s="138" cm="1">
         <f t="array" ref="AM14">SUM(AP17:AP65)+SUM(_xlfn._xlws.FILTER(AO17:AO65,AP17:AP65=""))+SUM(_xlfn._xlws.FILTER(AN17:AN65,(AO17:AO65="")*(AP17:AP65="")))</f>
         <v>0</v>
       </c>
-      <c r="AN14" s="141"/>
-      <c r="AO14" s="141"/>
-      <c r="AP14" s="141"/>
-      <c r="AQ14" s="142"/>
-      <c r="AR14" s="140" cm="1">
+      <c r="AN14" s="139"/>
+      <c r="AO14" s="139"/>
+      <c r="AP14" s="139"/>
+      <c r="AQ14" s="140"/>
+      <c r="AR14" s="138" cm="1">
         <f t="array" ref="AR14">SUM(AU17:AU65)+SUM(_xlfn._xlws.FILTER(AT17:AT65,AU17:AU65=""))+SUM(_xlfn._xlws.FILTER(AS17:AS65,(AT17:AT65="")*(AU17:AU65="")))</f>
         <v>0</v>
       </c>
-      <c r="AS14" s="141"/>
-      <c r="AT14" s="141"/>
-      <c r="AU14" s="141"/>
-      <c r="AV14" s="142"/>
-      <c r="AW14" s="140" cm="1">
+      <c r="AS14" s="139"/>
+      <c r="AT14" s="139"/>
+      <c r="AU14" s="139"/>
+      <c r="AV14" s="140"/>
+      <c r="AW14" s="138" cm="1">
         <f t="array" ref="AW14">SUM(AZ17:AZ65)+SUM(_xlfn._xlws.FILTER(AY17:AY65,AZ17:AZ65=""))+SUM(_xlfn._xlws.FILTER(AX17:AX65,(AY17:AY65="")*(AZ17:AZ65="")))</f>
         <v>0</v>
       </c>
-      <c r="AX14" s="141"/>
-      <c r="AY14" s="141"/>
-      <c r="AZ14" s="141"/>
-      <c r="BA14" s="142"/>
-      <c r="BB14" s="140" cm="1">
+      <c r="AX14" s="139"/>
+      <c r="AY14" s="139"/>
+      <c r="AZ14" s="139"/>
+      <c r="BA14" s="140"/>
+      <c r="BB14" s="138" cm="1">
         <f t="array" ref="BB14">SUM(BE17:BE65)+SUM(_xlfn._xlws.FILTER(BD17:BD65,BE17:BE65=""))+SUM(_xlfn._xlws.FILTER(BC17:BC65,(BD17:BD65="")*(BE17:BE65="")))</f>
         <v>0</v>
       </c>
-      <c r="BC14" s="141"/>
-      <c r="BD14" s="141"/>
-      <c r="BE14" s="141"/>
-      <c r="BF14" s="142"/>
-      <c r="BG14" s="140" cm="1">
+      <c r="BC14" s="139"/>
+      <c r="BD14" s="139"/>
+      <c r="BE14" s="139"/>
+      <c r="BF14" s="140"/>
+      <c r="BG14" s="138" cm="1">
         <f t="array" ref="BG14">SUM(BJ17:BJ65)+SUM(_xlfn._xlws.FILTER(BI17:BI65,BJ17:BJ65=""))+SUM(_xlfn._xlws.FILTER(BH17:BH65,(BI17:BI65="")*(BJ17:BJ65="")))</f>
         <v>0</v>
       </c>
-      <c r="BH14" s="141"/>
-      <c r="BI14" s="141"/>
-      <c r="BJ14" s="141"/>
-      <c r="BK14" s="142"/>
-      <c r="BL14" s="140" cm="1">
+      <c r="BH14" s="139"/>
+      <c r="BI14" s="139"/>
+      <c r="BJ14" s="139"/>
+      <c r="BK14" s="140"/>
+      <c r="BL14" s="138" cm="1">
         <f t="array" ref="BL14">SUM(BO17:BO65)+SUM(_xlfn._xlws.FILTER(BN17:BN65,BO17:BO65=""))+SUM(_xlfn._xlws.FILTER(BM17:BM65,(BN17:BN65="")*(BO17:BO65="")))</f>
         <v>0</v>
       </c>
-      <c r="BM14" s="141"/>
-      <c r="BN14" s="141"/>
-      <c r="BO14" s="141"/>
-      <c r="BP14" s="142"/>
-      <c r="BQ14" s="140" cm="1">
+      <c r="BM14" s="139"/>
+      <c r="BN14" s="139"/>
+      <c r="BO14" s="139"/>
+      <c r="BP14" s="140"/>
+      <c r="BQ14" s="138" cm="1">
         <f t="array" ref="BQ14">SUM(BT17:BT65)+SUM(_xlfn._xlws.FILTER(BS17:BS65,BT17:BT65=""))+SUM(_xlfn._xlws.FILTER(BR17:BR65,(BS17:BS65="")*(BT17:BT65="")))</f>
         <v>0</v>
       </c>
-      <c r="BR14" s="141"/>
-      <c r="BS14" s="141"/>
-      <c r="BT14" s="141"/>
-      <c r="BU14" s="142"/>
+      <c r="BR14" s="139"/>
+      <c r="BS14" s="139"/>
+      <c r="BT14" s="139"/>
+      <c r="BU14" s="140"/>
       <c r="BV14" s="16"/>
       <c r="BW14" s="17"/>
     </row>
@@ -3291,119 +3291,119 @@
         <f>SUBTOTAL(9,K17:K68)</f>
         <v>8537304.5</v>
       </c>
-      <c r="L15" s="147" t="s">
+      <c r="L15" s="150" t="s">
         <v>19</v>
       </c>
-      <c r="M15" s="148"/>
-      <c r="N15" s="149">
+      <c r="M15" s="151"/>
+      <c r="N15" s="141">
         <v>46053</v>
       </c>
-      <c r="O15" s="150" t="s">
+      <c r="O15" s="142" t="s">
         <v>20</v>
       </c>
-      <c r="P15" s="150"/>
-      <c r="Q15" s="150"/>
-      <c r="R15" s="150"/>
-      <c r="S15" s="149" t="s">
+      <c r="P15" s="142"/>
+      <c r="Q15" s="142"/>
+      <c r="R15" s="142"/>
+      <c r="S15" s="141" t="s">
         <v>21</v>
       </c>
-      <c r="T15" s="150"/>
-      <c r="U15" s="150"/>
-      <c r="V15" s="150"/>
-      <c r="W15" s="151"/>
-      <c r="X15" s="149">
+      <c r="T15" s="142"/>
+      <c r="U15" s="142"/>
+      <c r="V15" s="142"/>
+      <c r="W15" s="143"/>
+      <c r="X15" s="141">
         <v>46112</v>
       </c>
-      <c r="Y15" s="150" t="s">
+      <c r="Y15" s="142" t="s">
         <v>22</v>
       </c>
-      <c r="Z15" s="150"/>
-      <c r="AA15" s="150"/>
-      <c r="AB15" s="151"/>
-      <c r="AC15" s="149">
+      <c r="Z15" s="142"/>
+      <c r="AA15" s="142"/>
+      <c r="AB15" s="143"/>
+      <c r="AC15" s="141">
         <v>46142</v>
       </c>
-      <c r="AD15" s="150" t="s">
+      <c r="AD15" s="142" t="s">
         <v>23</v>
       </c>
-      <c r="AE15" s="150"/>
-      <c r="AF15" s="150"/>
-      <c r="AG15" s="151"/>
-      <c r="AH15" s="149">
+      <c r="AE15" s="142"/>
+      <c r="AF15" s="142"/>
+      <c r="AG15" s="143"/>
+      <c r="AH15" s="141">
         <v>46173</v>
       </c>
-      <c r="AI15" s="150" t="s">
+      <c r="AI15" s="142" t="s">
         <v>24</v>
       </c>
-      <c r="AJ15" s="150"/>
-      <c r="AK15" s="150"/>
-      <c r="AL15" s="151"/>
-      <c r="AM15" s="149">
+      <c r="AJ15" s="142"/>
+      <c r="AK15" s="142"/>
+      <c r="AL15" s="143"/>
+      <c r="AM15" s="141">
         <v>46203</v>
       </c>
-      <c r="AN15" s="150" t="s">
+      <c r="AN15" s="142" t="s">
         <v>25</v>
       </c>
-      <c r="AO15" s="150"/>
-      <c r="AP15" s="150"/>
-      <c r="AQ15" s="151"/>
-      <c r="AR15" s="149">
+      <c r="AO15" s="142"/>
+      <c r="AP15" s="142"/>
+      <c r="AQ15" s="143"/>
+      <c r="AR15" s="141">
         <v>46234</v>
       </c>
-      <c r="AS15" s="150" t="s">
+      <c r="AS15" s="142" t="s">
         <v>26</v>
       </c>
-      <c r="AT15" s="150"/>
-      <c r="AU15" s="150"/>
-      <c r="AV15" s="151"/>
-      <c r="AW15" s="149">
+      <c r="AT15" s="142"/>
+      <c r="AU15" s="142"/>
+      <c r="AV15" s="143"/>
+      <c r="AW15" s="141">
         <v>46265</v>
       </c>
-      <c r="AX15" s="150" t="s">
+      <c r="AX15" s="142" t="s">
         <v>27</v>
       </c>
-      <c r="AY15" s="150"/>
-      <c r="AZ15" s="150"/>
-      <c r="BA15" s="151"/>
-      <c r="BB15" s="149">
+      <c r="AY15" s="142"/>
+      <c r="AZ15" s="142"/>
+      <c r="BA15" s="143"/>
+      <c r="BB15" s="141">
         <v>46295</v>
       </c>
-      <c r="BC15" s="150" t="s">
+      <c r="BC15" s="142" t="s">
         <v>28</v>
       </c>
-      <c r="BD15" s="150"/>
-      <c r="BE15" s="150"/>
-      <c r="BF15" s="151"/>
-      <c r="BG15" s="149">
+      <c r="BD15" s="142"/>
+      <c r="BE15" s="142"/>
+      <c r="BF15" s="143"/>
+      <c r="BG15" s="141">
         <v>46326</v>
       </c>
-      <c r="BH15" s="150" t="s">
+      <c r="BH15" s="142" t="s">
         <v>29</v>
       </c>
-      <c r="BI15" s="150"/>
-      <c r="BJ15" s="150"/>
-      <c r="BK15" s="151"/>
-      <c r="BL15" s="149">
+      <c r="BI15" s="142"/>
+      <c r="BJ15" s="142"/>
+      <c r="BK15" s="143"/>
+      <c r="BL15" s="141">
         <v>46356</v>
       </c>
-      <c r="BM15" s="150" t="s">
+      <c r="BM15" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="BN15" s="150"/>
-      <c r="BO15" s="150"/>
-      <c r="BP15" s="151"/>
-      <c r="BQ15" s="149">
+      <c r="BN15" s="142"/>
+      <c r="BO15" s="142"/>
+      <c r="BP15" s="143"/>
+      <c r="BQ15" s="141">
         <v>46387</v>
       </c>
-      <c r="BR15" s="150" t="s">
+      <c r="BR15" s="142" t="s">
         <v>31</v>
       </c>
-      <c r="BS15" s="150"/>
-      <c r="BT15" s="150"/>
-      <c r="BU15" s="151"/>
+      <c r="BS15" s="142"/>
+      <c r="BT15" s="142"/>
+      <c r="BU15" s="143"/>
       <c r="BV15" s="19">
         <f>SUM(BV17:BV65)</f>
-        <v>556862.20000000007</v>
+        <v>535569.07000000007</v>
       </c>
       <c r="BW15" s="20"/>
       <c r="BY15" s="15"/>
@@ -3681,15 +3681,9 @@
       <c r="N17" s="91">
         <v>0</v>
       </c>
-      <c r="O17" s="34">
-        <v>10975</v>
-      </c>
-      <c r="P17" s="34">
-        <v>11347.01</v>
-      </c>
-      <c r="Q17" s="82">
-        <v>10656.33</v>
-      </c>
+      <c r="O17" s="34"/>
+      <c r="P17" s="34"/>
+      <c r="Q17" s="82"/>
       <c r="R17" s="36"/>
       <c r="S17" s="35"/>
       <c r="T17" s="34"/>
@@ -3748,7 +3742,7 @@
       <c r="BU17" s="42"/>
       <c r="BV17" s="35">
         <f t="shared" ref="BV17:BV65" si="0">SUM(IF(Q17&lt;&gt;"",Q17,IF(P17&lt;&gt;"",P17,O17)),IF(V17&lt;&gt;"",V17,IF(U17&lt;&gt;"",U17,T17)),IF(AA17&lt;&gt;"",AA17,IF(Z17&lt;&gt;"",Z17,Y17)),IF(AF17&lt;&gt;"",AF17,IF(AE17&lt;&gt;"",AE17,AD17)),IF(AK17&lt;&gt;"",AK17,IF(AJ17&lt;&gt;"",AJ17,AI17)),IF(AP17&lt;&gt;"",AP17,IF(AO17&lt;&gt;"",AO17,AN17)),IF(AU17&lt;&gt;"",AU17,IF(AT17&lt;&gt;"",AT17,AS17)),IF(AZ17&lt;&gt;"",AZ17,IF(AY17&lt;&gt;"",AY17,AX17)),IF(BE17&lt;&gt;"",BE17,IF(BD17&lt;&gt;"",BD17,BC17)),IF(BJ17&lt;&gt;"",BJ17,IF(BI17&lt;&gt;"",BI17,BH17)),IF(BO17&lt;&gt;"",BO17,IF(BN17&lt;&gt;"",BN17,BM17)),IF(BT17&lt;&gt;"",BT17,IF(BS17&lt;&gt;"",BS17,BR17)))</f>
-        <v>10656.33</v>
+        <v>0</v>
       </c>
       <c r="BW17" s="49"/>
       <c r="BX17" s="50"/>
@@ -3796,15 +3790,9 @@
       <c r="N18" s="92">
         <v>0</v>
       </c>
-      <c r="O18" s="39">
-        <v>10296</v>
-      </c>
-      <c r="P18" s="39">
-        <v>10548.89</v>
-      </c>
-      <c r="Q18" s="85">
-        <v>10636.8</v>
-      </c>
+      <c r="O18" s="39"/>
+      <c r="P18" s="39"/>
+      <c r="Q18" s="85"/>
       <c r="R18" s="41"/>
       <c r="S18" s="40"/>
       <c r="T18" s="39"/>
@@ -3863,7 +3851,7 @@
       <c r="BU18" s="42"/>
       <c r="BV18" s="35">
         <f t="shared" si="0"/>
-        <v>10636.8</v>
+        <v>0</v>
       </c>
       <c r="BW18" s="51"/>
       <c r="BX18" s="52"/>
@@ -8334,6 +8322,30 @@
   </sheetData>
   <autoFilter ref="A16:DD71" xr:uid="{177F1DEB-197D-49C6-A2E3-152C1AC7B373}"/>
   <mergeCells count="40">
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="BQ14:BU14"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="BB15:BF15"/>
+    <mergeCell ref="BG15:BK15"/>
+    <mergeCell ref="BL15:BP15"/>
+    <mergeCell ref="N14:R14"/>
+    <mergeCell ref="S14:W14"/>
+    <mergeCell ref="X14:AB14"/>
+    <mergeCell ref="AC14:AG14"/>
+    <mergeCell ref="AH14:AL14"/>
+    <mergeCell ref="AM14:AQ14"/>
+    <mergeCell ref="AR14:AV14"/>
+    <mergeCell ref="AW14:BA14"/>
+    <mergeCell ref="BB14:BF14"/>
+    <mergeCell ref="BG14:BK14"/>
+    <mergeCell ref="BL14:BP14"/>
+    <mergeCell ref="AC15:AG15"/>
+    <mergeCell ref="AH15:AL15"/>
+    <mergeCell ref="AM15:AQ15"/>
+    <mergeCell ref="AR15:AV15"/>
+    <mergeCell ref="AW15:BA15"/>
     <mergeCell ref="BQ13:BU13"/>
     <mergeCell ref="BQ15:BU15"/>
     <mergeCell ref="S13:W13"/>
@@ -8350,54 +8362,30 @@
     <mergeCell ref="S15:W15"/>
     <mergeCell ref="N15:R15"/>
     <mergeCell ref="X15:AB15"/>
-    <mergeCell ref="BB14:BF14"/>
-    <mergeCell ref="BG14:BK14"/>
-    <mergeCell ref="BL14:BP14"/>
-    <mergeCell ref="AC15:AG15"/>
-    <mergeCell ref="AH15:AL15"/>
-    <mergeCell ref="AM15:AQ15"/>
-    <mergeCell ref="AR15:AV15"/>
-    <mergeCell ref="AW15:BA15"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="BQ14:BU14"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="BB15:BF15"/>
-    <mergeCell ref="BG15:BK15"/>
-    <mergeCell ref="BL15:BP15"/>
-    <mergeCell ref="N14:R14"/>
-    <mergeCell ref="S14:W14"/>
-    <mergeCell ref="X14:AB14"/>
-    <mergeCell ref="AC14:AG14"/>
-    <mergeCell ref="AH14:AL14"/>
-    <mergeCell ref="AM14:AQ14"/>
-    <mergeCell ref="AR14:AV14"/>
-    <mergeCell ref="AW14:BA14"/>
   </mergeCells>
-  <conditionalFormatting sqref="Q65 V17:V65 AA17:AA65 AF17:AF65 AK17:AK65 AP17:AP65 AU17:AU65 AZ17:AZ65 BE17:BE65 BJ17:BJ65 BO17:BO65 BT17:BT65">
-    <cfRule type="expression" dxfId="4" priority="9">
+  <conditionalFormatting sqref="Q17:Q65">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>IF(AND(P17&gt;0,Q17=0),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="V17:V65 AA17:AA65 AF17:AF65 AK17:AK65 AP17:AP65 AU17:AU65 AZ17:AZ65 BE17:BE65 BJ17:BJ65 BO17:BO65 BT17:BT65">
+    <cfRule type="expression" dxfId="3" priority="9">
+      <formula>IF(AND(U17&gt;0,V17=0),TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="BT12 V17:X65 AB17:AC65 AG17:AH65 AL17:AM65 AQ17:AR65 AV17:AW65 BA17:BB65 BF17:BG65 BK17:BL65 BP17:BQ65 BU17:BU65">
-    <cfRule type="expression" dxfId="3" priority="10">
+    <cfRule type="expression" dxfId="2" priority="10">
       <formula>IF(AND(U12&lt;&gt;"",V12="",TODAY()&gt;DATE(YEAR(TODAY()),MONTH(DATEVALUE("1-"&amp;LEFT(#REF!,3)&amp;"-1900")),20)),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BV17:BV64">
-    <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="greaterThan">
       <formula>90%*$K$17</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BW13:BW14">
-    <cfRule type="expression" dxfId="1" priority="8">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>IF(BW13&lt;0,TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q17:Q64">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>IF(AND(P17&gt;0,Q17=0),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8408,6 +8396,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100705CE5A564F40946AECC6EBE58791375" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8ba3a2bde39cc3ca0702cdfcb4eca37d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ca7236cb-6f9c-48f7-87fd-cb400629eee9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="22de7e6ac394ce7397beb0dba85b4d79" ns2:_="">
     <xsd:import namespace="ca7236cb-6f9c-48f7-87fd-cb400629eee9"/>
@@ -8569,35 +8572,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD946F0F-13D5-444C-A93C-86A02D792EE0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3614A8F8-9AED-4C02-B640-81A3A1FEB080}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="ca7236cb-6f9c-48f7-87fd-cb400629eee9"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8619,9 +8597,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3614A8F8-9AED-4C02-B640-81A3A1FEB080}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD946F0F-13D5-444C-A93C-86A02D792EE0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ca7236cb-6f9c-48f7-87fd-cb400629eee9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>